--- a/Semiconductor/SWKS.xlsx
+++ b/Semiconductor/SWKS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameel/Library/CloudStorage/Dropbox/models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B871A68-D0BB-D04E-AC84-5AD1C114AC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48666112-59E4-CB49-89D8-D2D299A4E94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13300" yWindow="1980" windowWidth="27640" windowHeight="16940" xr2:uid="{872DC379-8029-6E4A-AB13-AE0B132249A5}"/>
+    <workbookView xWindow="20820" yWindow="3540" windowWidth="30380" windowHeight="18980" activeTab="1" xr2:uid="{872DC379-8029-6E4A-AB13-AE0B132249A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t>P</t>
   </si>
@@ -175,18 +175,97 @@
   </si>
   <si>
     <t>OM</t>
+  </si>
+  <si>
+    <t>HQ: Irvine, CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash </t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventory </t>
+  </si>
+  <si>
+    <t>PPE</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>OA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Assets </t>
+  </si>
+  <si>
+    <t>A/P</t>
+  </si>
+  <si>
+    <t>Accrued</t>
+  </si>
+  <si>
+    <t>Debt</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>TL + E</t>
+  </si>
+  <si>
+    <t>CFFO</t>
+  </si>
+  <si>
+    <t>Capex</t>
+  </si>
+  <si>
+    <t>FCF</t>
+  </si>
+  <si>
+    <t>4Q Moving FCF</t>
+  </si>
+  <si>
+    <t>4Q Moving NI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NI </t>
+  </si>
+  <si>
+    <t>Shares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Cash </t>
+  </si>
+  <si>
+    <t>DPO</t>
+  </si>
+  <si>
+    <t>DSO</t>
+  </si>
+  <si>
+    <t>DIO</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>ROIC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -209,16 +288,29 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -226,23 +318,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -265,16 +400,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -289,8 +424,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5156200" y="76200"/>
-          <a:ext cx="50800" cy="11988800"/>
+          <a:off x="6299200" y="12700"/>
+          <a:ext cx="50800" cy="12192000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -315,15 +450,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -339,8 +474,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="13385800" y="0"/>
-          <a:ext cx="50800" cy="12192000"/>
+          <a:off x="14262100" y="0"/>
+          <a:ext cx="50800" cy="12598400"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -683,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2208B4-D5F3-2D42-AF5A-21BE16CD29C2}">
-  <dimension ref="B2:F16"/>
+  <dimension ref="B2:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="30.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.83203125" style="3" customWidth="1"/>
@@ -691,15 +826,16 @@
     <col min="3" max="4" width="30.33203125" style="3"/>
     <col min="5" max="5" width="4" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="30.33203125" style="3"/>
+    <col min="7" max="7" width="5.33203125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="30.33203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
@@ -710,42 +846,56 @@
         <v>74.510000000000005</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="E4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="3">
-        <v>148.42756800000001</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+        <v>150.37361200000001</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="3">
         <f>+F3*F4</f>
-        <v>11059.338091680002</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+        <v>11204.337830120001</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="3">
-        <f>1185.9+132</f>
-        <v>1317.9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+        <f>1550.4+8.3</f>
+        <v>1558.7</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <f>+G4</f>
+        <v>Q126</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="3">
-        <f>499.2+496.2</f>
-        <v>995.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+        <f>499.6+496.6</f>
+        <v>996.2</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <f>+G6</f>
+        <v>Q126</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
@@ -754,21 +904,21 @@
       </c>
       <c r="F8" s="3">
         <f>+F5-F6+F7</f>
-        <v>10736.838091680002</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+        <v>10641.837830120001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -782,18 +932,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B10BAA6-AB93-1A44-BE3C-6AF20F9000FE}">
-  <dimension ref="B3:XFD30"/>
+  <dimension ref="B2:XFD65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="5.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="7.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="5.5" style="15" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="10.83203125" style="2"/>
     <col min="17" max="23" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="36" width="7.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -806,41 +955,72 @@
     <col min="16384" max="16384" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:236 16384:16384" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11">
+        <v>45380</v>
+      </c>
+      <c r="E2" s="11">
+        <f>+I2-365</f>
+        <v>45470</v>
+      </c>
+      <c r="F2" s="11">
+        <v>45562</v>
+      </c>
+      <c r="G2" s="11">
+        <v>45653</v>
+      </c>
+      <c r="H2" s="11">
+        <v>45744</v>
+      </c>
+      <c r="I2" s="11">
+        <v>45835</v>
+      </c>
+      <c r="J2" s="11">
+        <v>45933</v>
+      </c>
+      <c r="K2" s="11">
+        <v>46055</v>
+      </c>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+    </row>
     <row r="3" spans="2:236 16384:16384" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="12" t="s">
         <v>20</v>
       </c>
       <c r="Q3" s="1">
@@ -851,7 +1031,7 @@
         <v>2016</v>
       </c>
       <c r="S3" s="1">
-        <f t="shared" ref="S3:AP3" si="0">+R3+1</f>
+        <f t="shared" ref="S3:AK3" si="0">+R3+1</f>
         <v>2017</v>
       </c>
       <c r="T3" s="1">
@@ -1707,7 +1887,7 @@
         <v>2230</v>
       </c>
       <c r="HY3" s="1">
-        <f t="shared" ref="HY3:ID3" si="5">+HX3+1</f>
+        <f t="shared" ref="HY3:IB3" si="5">+HX3+1</f>
         <v>2231</v>
       </c>
       <c r="HZ3" s="1">
@@ -1731,6 +1911,18 @@
       <c r="B4" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
       <c r="X4" s="4">
         <v>0.57999999999999996</v>
       </c>
@@ -1741,116 +1933,162 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="5" spans="2:236 16384:16384" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="2:236 16384:16384" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+    </row>
     <row r="6" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="18">
         <v>1201.5</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="18">
         <v>1046</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="18">
         <v>905.5</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="18">
         <f>+Z6-SUM(C6:E6)</f>
         <v>1025</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="18">
         <v>1068.5</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="18">
         <v>953.2</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="18">
         <v>965</v>
       </c>
-      <c r="J6" s="2">
-        <f>AVERAGE(1,1.03) * 10^3</f>
-        <v>1015.0000000000001</v>
-      </c>
-      <c r="X6" s="2">
+      <c r="J6" s="18">
+        <v>1100.2</v>
+      </c>
+      <c r="K6" s="18">
+        <v>1035.4000000000001</v>
+      </c>
+      <c r="L6" s="18">
+        <f>AVERAGE(875,925)</f>
+        <v>900</v>
+      </c>
+      <c r="M6" s="18">
+        <f>+I6</f>
+        <v>965</v>
+      </c>
+      <c r="N6" s="18">
+        <f>+M6</f>
+        <v>965</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17">
         <v>5485.5</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6" s="17">
         <v>4772.3999999999996</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6" s="17">
         <v>4178</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6" s="17">
         <f>SUM(G6:J6)</f>
-        <v>4001.7</v>
-      </c>
-      <c r="AB6" s="2">
-        <f>+AA6*1.03</f>
-        <v>4121.7510000000002</v>
-      </c>
-      <c r="AC6" s="2">
-        <f t="shared" ref="AC6:AJ6" si="7">+AB6*1.03</f>
-        <v>4245.4035300000005</v>
-      </c>
-      <c r="AD6" s="2">
+        <v>4086.8999999999996</v>
+      </c>
+      <c r="AB6" s="17">
+        <f>+AA6*0.98</f>
+        <v>4005.1619999999994</v>
+      </c>
+      <c r="AC6" s="17">
+        <f t="shared" ref="AC6:AJ6" si="7">+AB6*0.98</f>
+        <v>3925.0587599999994</v>
+      </c>
+      <c r="AD6" s="17">
         <f t="shared" si="7"/>
-        <v>4372.7656359000002</v>
-      </c>
-      <c r="AE6" s="2">
+        <v>3846.5575847999994</v>
+      </c>
+      <c r="AE6" s="17">
         <f t="shared" si="7"/>
-        <v>4503.9486049770003</v>
-      </c>
-      <c r="AF6" s="2">
+        <v>3769.6264331039993</v>
+      </c>
+      <c r="AF6" s="17">
         <f t="shared" si="7"/>
-        <v>4639.0670631263101</v>
-      </c>
-      <c r="AG6" s="2">
+        <v>3694.2339044419191</v>
+      </c>
+      <c r="AG6" s="17">
         <f t="shared" si="7"/>
-        <v>4778.2390750200993</v>
-      </c>
-      <c r="AH6" s="2">
+        <v>3620.3492263530807</v>
+      </c>
+      <c r="AH6" s="17">
         <f t="shared" si="7"/>
-        <v>4921.5862472707022</v>
-      </c>
-      <c r="AI6" s="2">
+        <v>3547.9422418260192</v>
+      </c>
+      <c r="AI6" s="17">
         <f t="shared" si="7"/>
-        <v>5069.2338346888237</v>
-      </c>
-      <c r="AJ6" s="2">
+        <v>3476.9833969894989</v>
+      </c>
+      <c r="AJ6" s="17">
         <f t="shared" si="7"/>
-        <v>5221.3108497294888</v>
-      </c>
+        <v>3407.443729049709</v>
+      </c>
+      <c r="AK6" s="17"/>
+      <c r="AL6" s="17"/>
+      <c r="AM6" s="17"/>
+      <c r="AN6" s="17"/>
     </row>
     <row r="7" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="15">
         <v>694.9</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="15">
         <v>625.70000000000005</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="15">
         <v>541.4</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="15">
         <f t="shared" ref="F7:F16" si="8">+Z7-SUM(C7:E7)</f>
         <v>595.19999999999982</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="15">
         <v>626.6</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="15">
         <v>561.6</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="15">
         <v>564</v>
       </c>
-      <c r="J7" s="2">
-        <f>+J6*(1-AVERAGE(G20:I20))</f>
-        <v>595.48657544208925</v>
+      <c r="J7" s="15">
+        <v>652.6</v>
+      </c>
+      <c r="K7" s="15">
+        <v>608.20000000000005</v>
+      </c>
+      <c r="L7" s="15">
+        <f>+L$6*(G7/G$6)</f>
+        <v>527.78661675245667</v>
       </c>
       <c r="X7" s="2">
         <v>2881.2</v>
@@ -1863,80 +2101,88 @@
       </c>
       <c r="AA7" s="2">
         <f t="shared" ref="AA7:AA16" si="9">SUM(G7:J7)</f>
-        <v>2347.6865754420892</v>
+        <v>2404.8000000000002</v>
       </c>
       <c r="AB7" s="2">
         <f>+AB$6*(AA7/AA$6)</f>
-        <v>2418.117172705352</v>
+        <v>2356.7039999999997</v>
       </c>
       <c r="AC7" s="2">
         <f t="shared" ref="AC7:AJ13" si="10">+AC$6*(AB7/AB$6)</f>
-        <v>2490.6606878865127</v>
+        <v>2309.5699199999999</v>
       </c>
       <c r="AD7" s="2">
         <f t="shared" si="10"/>
-        <v>2565.3805085231083</v>
+        <v>2263.3785216000001</v>
       </c>
       <c r="AE7" s="2">
         <f t="shared" si="10"/>
-        <v>2642.3419237788016</v>
+        <v>2218.1109511679997</v>
       </c>
       <c r="AF7" s="2">
         <f t="shared" si="10"/>
-        <v>2721.6121814921653</v>
+        <v>2173.7487321446397</v>
       </c>
       <c r="AG7" s="2">
         <f t="shared" si="10"/>
-        <v>2803.26054693693</v>
+        <v>2130.2737575017468</v>
       </c>
       <c r="AH7" s="2">
         <f t="shared" si="10"/>
-        <v>2887.358363345038</v>
+        <v>2087.6682823517122</v>
       </c>
       <c r="AI7" s="2">
         <f t="shared" si="10"/>
-        <v>2973.9791142453896</v>
+        <v>2045.914916704678</v>
       </c>
       <c r="AJ7" s="2">
         <f t="shared" si="10"/>
-        <v>3063.1984876727515</v>
+        <v>2004.9966183705844</v>
       </c>
     </row>
     <row r="8" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="15">
         <f>+C6-C7</f>
         <v>506.6</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="15">
         <f>+D6-D7</f>
         <v>420.29999999999995</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="15">
         <f>+E6-E7</f>
         <v>364.1</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="15">
         <f t="shared" si="8"/>
         <v>429.80000000000018</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="15">
         <f>+G6-G7</f>
         <v>441.9</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="15">
         <f>+H6-H7</f>
         <v>391.6</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="15">
         <f>+I6-I7</f>
         <v>401</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="15">
         <f>+J6-J7</f>
-        <v>419.51342455791087</v>
+        <v>447.6</v>
+      </c>
+      <c r="K8" s="15">
+        <f>+K6-K7</f>
+        <v>427.20000000000005</v>
+      </c>
+      <c r="L8" s="15">
+        <f>+L6-L7</f>
+        <v>372.21338324754333</v>
       </c>
       <c r="X8" s="2">
         <f>+X6-X7</f>
@@ -1952,74 +2198,80 @@
       </c>
       <c r="AA8" s="2">
         <f t="shared" si="9"/>
-        <v>1654.0134245579109</v>
+        <v>1682.1</v>
       </c>
       <c r="AB8" s="2">
         <f>+AB6-AB7</f>
-        <v>1703.6338272946482</v>
+        <v>1648.4579999999996</v>
       </c>
       <c r="AC8" s="2">
         <f t="shared" ref="AC8:AJ8" si="11">+AC6-AC7</f>
-        <v>1754.7428421134878</v>
+        <v>1615.4888399999995</v>
       </c>
       <c r="AD8" s="2">
         <f t="shared" si="11"/>
-        <v>1807.3851273768919</v>
+        <v>1583.1790631999993</v>
       </c>
       <c r="AE8" s="2">
         <f t="shared" si="11"/>
-        <v>1861.6066811981987</v>
+        <v>1551.5154819359996</v>
       </c>
       <c r="AF8" s="2">
         <f t="shared" si="11"/>
-        <v>1917.4548816341448</v>
+        <v>1520.4851722972794</v>
       </c>
       <c r="AG8" s="2">
         <f t="shared" si="11"/>
-        <v>1974.9785280831693</v>
+        <v>1490.0754688513339</v>
       </c>
       <c r="AH8" s="2">
         <f t="shared" si="11"/>
-        <v>2034.2278839256642</v>
+        <v>1460.273959474307</v>
       </c>
       <c r="AI8" s="2">
         <f t="shared" si="11"/>
-        <v>2095.2547204434341</v>
+        <v>1431.0684802848209</v>
       </c>
       <c r="AJ8" s="2">
         <f t="shared" si="11"/>
-        <v>2158.1123620567373</v>
+        <v>1402.4471106791245</v>
       </c>
     </row>
     <row r="9" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="15">
         <v>153.1</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="15">
         <v>154.4</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="15">
         <v>160.69999999999999</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="15">
         <f t="shared" si="8"/>
         <v>163.50000000000006</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="15">
         <v>176.4</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="15">
         <v>186.5</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="15">
         <v>199.4</v>
       </c>
-      <c r="J9" s="2">
-        <f>+J$6*(I9/I$6)</f>
-        <v>209.73160621761662</v>
+      <c r="J9" s="15">
+        <v>223.1</v>
+      </c>
+      <c r="K9" s="15">
+        <v>203.4</v>
+      </c>
+      <c r="L9" s="15">
+        <f>+L$6*(G9/G$6)</f>
+        <v>148.58212447356107</v>
       </c>
       <c r="X9" s="2">
         <v>617.9</v>
@@ -2032,74 +2284,80 @@
       </c>
       <c r="AA9" s="2">
         <f t="shared" si="9"/>
-        <v>772.03160621761663</v>
+        <v>785.4</v>
       </c>
       <c r="AB9" s="2">
         <f>+AB$6*(AA9/AA$6)</f>
-        <v>795.1925544041452</v>
+        <v>769.69199999999989</v>
       </c>
       <c r="AC9" s="2">
         <f t="shared" si="10"/>
-        <v>819.0483310362697</v>
+        <v>754.29815999999994</v>
       </c>
       <c r="AD9" s="2">
         <f t="shared" si="10"/>
-        <v>843.61978096735766</v>
+        <v>739.2121967999999</v>
       </c>
       <c r="AE9" s="2">
         <f t="shared" si="10"/>
-        <v>868.92837439637844</v>
+        <v>724.42795286399985</v>
       </c>
       <c r="AF9" s="2">
         <f t="shared" si="10"/>
-        <v>894.99622562826971</v>
+        <v>709.93939380671986</v>
       </c>
       <c r="AG9" s="2">
         <f t="shared" si="10"/>
-        <v>921.84611239711785</v>
+        <v>695.74060593058539</v>
       </c>
       <c r="AH9" s="2">
         <f t="shared" si="10"/>
-        <v>949.50149576903129</v>
+        <v>681.82579381197365</v>
       </c>
       <c r="AI9" s="2">
         <f t="shared" si="10"/>
-        <v>977.98654064210234</v>
+        <v>668.18927793573425</v>
       </c>
       <c r="AJ9" s="2">
         <f t="shared" si="10"/>
-        <v>1007.3261368613655</v>
+        <v>654.82549237701949</v>
       </c>
     </row>
     <row r="10" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="15">
         <v>78.8</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="15">
         <v>76.8</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="15">
         <v>71.2</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="15">
         <f t="shared" si="8"/>
         <v>74</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="15">
         <v>82.6</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="15">
         <v>88</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="15">
         <v>89.3</v>
       </c>
-      <c r="J10" s="2">
-        <f>+J$6*(I10/I$6)</f>
-        <v>93.926943005181357</v>
+      <c r="J10" s="15">
+        <v>111.7</v>
+      </c>
+      <c r="K10" s="15">
+        <v>108.4</v>
+      </c>
+      <c r="L10" s="15">
+        <f>+L$6*(G10/G$6)</f>
+        <v>69.574169396350015</v>
       </c>
       <c r="X10" s="2">
         <v>329.8</v>
@@ -2112,80 +2370,88 @@
       </c>
       <c r="AA10" s="2">
         <f t="shared" si="9"/>
-        <v>353.82694300518131</v>
+        <v>371.59999999999997</v>
       </c>
       <c r="AB10" s="2">
         <f>+AB$6*(AA10/AA$6)</f>
-        <v>364.44175129533681</v>
+        <v>364.16799999999995</v>
       </c>
       <c r="AC10" s="2">
         <f t="shared" si="10"/>
-        <v>375.37500383419695</v>
+        <v>356.88463999999993</v>
       </c>
       <c r="AD10" s="2">
         <f t="shared" si="10"/>
-        <v>386.63625394922281</v>
+        <v>349.74694719999997</v>
       </c>
       <c r="AE10" s="2">
         <f t="shared" si="10"/>
-        <v>398.23534156769949</v>
+        <v>342.75200825599995</v>
       </c>
       <c r="AF10" s="2">
         <f t="shared" si="10"/>
-        <v>410.18240181473044</v>
+        <v>335.89696809087991</v>
       </c>
       <c r="AG10" s="2">
         <f t="shared" si="10"/>
-        <v>422.48787386917235</v>
+        <v>329.17902872906234</v>
       </c>
       <c r="AH10" s="2">
         <f t="shared" si="10"/>
-        <v>435.16251008524756</v>
+        <v>322.59544815448106</v>
       </c>
       <c r="AI10" s="2">
         <f t="shared" si="10"/>
-        <v>448.217385387805</v>
+        <v>316.14353919139148</v>
       </c>
       <c r="AJ10" s="2">
         <f t="shared" si="10"/>
-        <v>461.66390694943919</v>
+        <v>309.82066840756363</v>
       </c>
     </row>
     <row r="11" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="15">
         <f>+C8-SUM(C9:C10)</f>
         <v>274.70000000000005</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="15">
         <f>+D8-SUM(D9:D10)</f>
         <v>189.09999999999997</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="15">
         <f>+E8-SUM(E9:E10)</f>
         <v>132.20000000000005</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="15">
         <f t="shared" si="8"/>
         <v>192.30000000000018</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="15">
         <f>+G8-SUM(G9:G10)</f>
         <v>182.89999999999998</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="15">
         <f>+H8-SUM(H9:H10)</f>
         <v>117.10000000000002</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="15">
         <f>+I8-SUM(I9:I10)</f>
         <v>112.30000000000001</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="15">
         <f>+J8-SUM(J9:J10)</f>
-        <v>115.85487533511287</v>
+        <v>112.80000000000001</v>
+      </c>
+      <c r="K11" s="15">
+        <f>+K8-SUM(K9:K10)</f>
+        <v>115.40000000000003</v>
+      </c>
+      <c r="L11" s="15">
+        <f>+L8-SUM(L9:L10)</f>
+        <v>154.05708937763225</v>
       </c>
       <c r="X11" s="2">
         <f>+X8-SUM(X9:X10)</f>
@@ -2201,74 +2467,80 @@
       </c>
       <c r="AA11" s="2">
         <f t="shared" si="9"/>
-        <v>528.15487533511282</v>
+        <v>525.1</v>
       </c>
       <c r="AB11" s="2">
         <f>+AB8-SUM(AB9:AB10)</f>
-        <v>543.99952159516624</v>
+        <v>514.59799999999973</v>
       </c>
       <c r="AC11" s="2">
         <f t="shared" ref="AC11:AJ11" si="12">+AC8-SUM(AC9:AC10)</f>
-        <v>560.31950724302123</v>
+        <v>504.30603999999971</v>
       </c>
       <c r="AD11" s="2">
         <f t="shared" si="12"/>
-        <v>577.12909246031131</v>
+        <v>494.21991919999937</v>
       </c>
       <c r="AE11" s="2">
         <f t="shared" si="12"/>
-        <v>594.44296523412072</v>
+        <v>484.33552081599964</v>
       </c>
       <c r="AF11" s="2">
         <f t="shared" si="12"/>
-        <v>612.27625419114474</v>
+        <v>474.64881039967963</v>
       </c>
       <c r="AG11" s="2">
         <f t="shared" si="12"/>
-        <v>630.64454181687915</v>
+        <v>465.15583419168615</v>
       </c>
       <c r="AH11" s="2">
         <f t="shared" si="12"/>
-        <v>649.56387807138526</v>
+        <v>455.85271750785228</v>
       </c>
       <c r="AI11" s="2">
         <f t="shared" si="12"/>
-        <v>669.05079441352677</v>
+        <v>446.73566315769517</v>
       </c>
       <c r="AJ11" s="2">
         <f t="shared" si="12"/>
-        <v>689.12231824593255</v>
+        <v>437.80094989454142</v>
       </c>
     </row>
     <row r="12" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="15">
         <v>-10</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="15">
         <v>-7.1</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="15">
         <v>-6.6</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="15">
         <f t="shared" si="8"/>
         <v>-6.9999999999999964</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="15">
         <v>-6.8</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="15">
         <v>-6.8</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="15">
         <v>-6.6</v>
       </c>
-      <c r="J12" s="2">
-        <f>+J$11*(I12/I$11)</f>
-        <v>-6.8089241069612179</v>
+      <c r="J12" s="15">
+        <v>-6.8</v>
+      </c>
+      <c r="K12" s="15">
+        <v>-6.3</v>
+      </c>
+      <c r="L12" s="15">
+        <f>+L$11*(G12/G$11)</f>
+        <v>-5.7276555919513363</v>
       </c>
       <c r="X12" s="2">
         <v>-47.9</v>
@@ -2281,74 +2553,80 @@
       </c>
       <c r="AA12" s="2">
         <f t="shared" si="9"/>
-        <v>-27.008924106961217</v>
+        <v>-27</v>
       </c>
       <c r="AB12" s="2">
         <f>+AB$6*(AA12/AA$6)</f>
-        <v>-27.819191830170059</v>
+        <v>-26.459999999999997</v>
       </c>
       <c r="AC12" s="2">
         <f t="shared" si="10"/>
-        <v>-28.653767585075162</v>
+        <v>-25.930799999999998</v>
       </c>
       <c r="AD12" s="2">
         <f t="shared" si="10"/>
-        <v>-29.513380612627415</v>
+        <v>-25.412183999999996</v>
       </c>
       <c r="AE12" s="2">
         <f t="shared" si="10"/>
-        <v>-30.398782031006238</v>
+        <v>-24.903940319999997</v>
       </c>
       <c r="AF12" s="2">
         <f t="shared" si="10"/>
-        <v>-31.310745491936423</v>
+        <v>-24.405861513599994</v>
       </c>
       <c r="AG12" s="2">
         <f t="shared" si="10"/>
-        <v>-32.250067856694514</v>
+        <v>-23.917744283327995</v>
       </c>
       <c r="AH12" s="2">
         <f t="shared" si="10"/>
-        <v>-33.217569892395346</v>
+        <v>-23.439389397661436</v>
       </c>
       <c r="AI12" s="2">
         <f t="shared" si="10"/>
-        <v>-34.21409698916721</v>
+        <v>-22.970601609708208</v>
       </c>
       <c r="AJ12" s="2">
         <f t="shared" si="10"/>
-        <v>-35.24051989884223</v>
+        <v>-22.511189577514042</v>
       </c>
     </row>
     <row r="13" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="15">
         <v>3.4</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="15">
         <v>10.8</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="15">
         <v>9.6</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="15">
         <f t="shared" si="8"/>
         <v>5.8999999999999986</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="15">
         <v>16.100000000000001</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="15">
         <v>11.9</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="15">
         <v>8</v>
       </c>
-      <c r="J13" s="2">
-        <f>+J$11*(I13/I$11)</f>
-        <v>8.2532413417711741</v>
+      <c r="J13" s="15">
+        <v>17.8</v>
+      </c>
+      <c r="K13" s="15">
+        <v>12.2</v>
+      </c>
+      <c r="L13" s="15">
+        <f>+L$11*(G13/G$11)</f>
+        <v>13.561066916237726</v>
       </c>
       <c r="X13" s="2">
         <v>-2.5</v>
@@ -2361,80 +2639,88 @@
       </c>
       <c r="AA13" s="2">
         <f t="shared" si="9"/>
-        <v>44.253241341771172</v>
+        <v>53.8</v>
       </c>
       <c r="AB13" s="2">
         <f>+AB$6*(AA13/AA$6)</f>
-        <v>45.580838582024306</v>
+        <v>52.72399999999999</v>
       </c>
       <c r="AC13" s="2">
         <f t="shared" si="10"/>
-        <v>46.948263739485043</v>
+        <v>51.669519999999991</v>
       </c>
       <c r="AD13" s="2">
         <f t="shared" si="10"/>
-        <v>48.356711651669592</v>
+        <v>50.636129599999997</v>
       </c>
       <c r="AE13" s="2">
         <f t="shared" si="10"/>
-        <v>49.807413001219679</v>
+        <v>49.623407007999994</v>
       </c>
       <c r="AF13" s="2">
         <f t="shared" si="10"/>
-        <v>51.301635391256269</v>
+        <v>48.630938867839987</v>
       </c>
       <c r="AG13" s="2">
         <f t="shared" si="10"/>
-        <v>52.840684452993955</v>
+        <v>47.658320090483187</v>
       </c>
       <c r="AH13" s="2">
         <f t="shared" si="10"/>
-        <v>54.425904986583774</v>
+        <v>46.705153688673526</v>
       </c>
       <c r="AI13" s="2">
         <f t="shared" si="10"/>
-        <v>56.058682136181289</v>
+        <v>45.771050614900055</v>
       </c>
       <c r="AJ13" s="2">
         <f t="shared" si="10"/>
-        <v>57.740442600266732</v>
+        <v>44.85562960260205</v>
       </c>
     </row>
     <row r="14" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="15">
         <f>+SUM(C11:C13)</f>
         <v>268.10000000000002</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="15">
         <f>+SUM(D11:D13)</f>
         <v>192.79999999999998</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="15">
         <f>+SUM(E11:E13)</f>
         <v>135.20000000000005</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="15">
         <f t="shared" si="8"/>
         <v>191.20000000000016</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="15">
         <f>+SUM(G11:G13)</f>
         <v>192.19999999999996</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="15">
         <f>+SUM(H11:H13)</f>
         <v>122.20000000000003</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="15">
         <f>+SUM(I11:I13)</f>
         <v>113.70000000000002</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="15">
         <f>+SUM(J11:J13)</f>
-        <v>117.29919256992282</v>
+        <v>123.80000000000001</v>
+      </c>
+      <c r="K14" s="15">
+        <f>+SUM(K11:K13)</f>
+        <v>121.30000000000004</v>
+      </c>
+      <c r="L14" s="15">
+        <f>+SUM(L11:L13)</f>
+        <v>161.89050070191865</v>
       </c>
       <c r="X14" s="2">
         <f>+SUM(X11:X13)</f>
@@ -2450,74 +2736,80 @@
       </c>
       <c r="AA14" s="2">
         <f t="shared" si="9"/>
-        <v>545.39919256992289</v>
+        <v>551.90000000000009</v>
       </c>
       <c r="AB14" s="2">
         <f>+SUM(AB11:AB13)</f>
-        <v>561.76116834702043</v>
+        <v>540.86199999999974</v>
       </c>
       <c r="AC14" s="2">
         <f t="shared" ref="AC14:AJ14" si="13">+SUM(AC11:AC13)</f>
-        <v>578.61400339743113</v>
+        <v>530.04475999999977</v>
       </c>
       <c r="AD14" s="2">
         <f t="shared" si="13"/>
-        <v>595.97242349935345</v>
+        <v>519.44386479999935</v>
       </c>
       <c r="AE14" s="2">
         <f t="shared" si="13"/>
-        <v>613.8515962043341</v>
+        <v>509.05498750399966</v>
       </c>
       <c r="AF14" s="2">
         <f t="shared" si="13"/>
-        <v>632.26714409046451</v>
+        <v>498.87388775391963</v>
       </c>
       <c r="AG14" s="2">
         <f t="shared" si="13"/>
-        <v>651.23515841317862</v>
+        <v>488.89640999884136</v>
       </c>
       <c r="AH14" s="2">
         <f t="shared" si="13"/>
-        <v>670.7722131655737</v>
+        <v>479.11848179886437</v>
       </c>
       <c r="AI14" s="2">
         <f t="shared" si="13"/>
-        <v>690.89537956054096</v>
+        <v>469.53611216288704</v>
       </c>
       <c r="AJ14" s="2">
         <f t="shared" si="13"/>
-        <v>711.62224094735711</v>
+        <v>460.14538991962945</v>
       </c>
     </row>
     <row r="15" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="15">
         <v>20.399999999999999</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="15">
         <v>9.3000000000000007</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="15">
         <v>12.5</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="15">
         <f t="shared" si="8"/>
         <v>-1.8000000000000043</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="15">
         <v>28.4</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="15">
         <v>33.700000000000003</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="15">
         <v>7</v>
       </c>
-      <c r="J15" s="2">
-        <f>+J14*(I15/I14)</f>
-        <v>7.2215861740497775</v>
+      <c r="J15" s="15">
+        <v>-19.399999999999999</v>
+      </c>
+      <c r="K15" s="15">
+        <v>30.5</v>
+      </c>
+      <c r="L15" s="15">
+        <f>+L14*0.25</f>
+        <v>40.472625175479664</v>
       </c>
       <c r="X15" s="2">
         <v>201.4</v>
@@ -2530,80 +2822,88 @@
       </c>
       <c r="AA15" s="2">
         <f t="shared" si="9"/>
-        <v>76.32158617404977</v>
+        <v>49.699999999999996</v>
       </c>
       <c r="AB15" s="2">
         <f>+AB14*(AA15/AA14)</f>
-        <v>78.611233759271244</v>
+        <v>48.705999999999968</v>
       </c>
       <c r="AC15" s="2">
         <f t="shared" ref="AC15:AJ15" si="14">+AC14*(AB15/AB14)</f>
-        <v>80.969570772049394</v>
+        <v>47.731879999999968</v>
       </c>
       <c r="AD15" s="2">
         <f t="shared" si="14"/>
-        <v>83.398657895210789</v>
+        <v>46.777242399999935</v>
       </c>
       <c r="AE15" s="2">
         <f t="shared" si="14"/>
-        <v>85.90061763206711</v>
+        <v>45.841697551999957</v>
       </c>
       <c r="AF15" s="2">
         <f t="shared" si="14"/>
-        <v>88.477636161029181</v>
+        <v>44.924863600959959</v>
       </c>
       <c r="AG15" s="2">
         <f t="shared" si="14"/>
-        <v>91.131965245860087</v>
+        <v>44.026366328940767</v>
       </c>
       <c r="AH15" s="2">
         <f t="shared" si="14"/>
-        <v>93.865924203235849</v>
+        <v>43.145839002361939</v>
       </c>
       <c r="AI15" s="2">
         <f t="shared" si="14"/>
-        <v>96.681901929332923</v>
+        <v>42.282922222314696</v>
       </c>
       <c r="AJ15" s="2">
         <f t="shared" si="14"/>
-        <v>99.582358987212913</v>
+        <v>41.437263777868417</v>
       </c>
     </row>
     <row r="16" spans="2:236 16384:16384" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="15">
         <f>+C14-C15</f>
         <v>247.70000000000002</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="15">
         <f>+D14-D15</f>
         <v>183.49999999999997</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="15">
         <f>+E14-E15</f>
         <v>122.70000000000005</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="15">
         <f t="shared" si="8"/>
         <v>193.00000000000011</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="15">
         <f>+G14-G15</f>
         <v>163.79999999999995</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="15">
         <f>+H14-H15</f>
         <v>88.500000000000028</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="15">
         <f>+I14-I15</f>
         <v>106.70000000000002</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="15">
         <f>+J14-J15</f>
-        <v>110.07760639587305</v>
+        <v>143.20000000000002</v>
+      </c>
+      <c r="K16" s="15">
+        <f>+K14-K15</f>
+        <v>90.80000000000004</v>
+      </c>
+      <c r="L16" s="15">
+        <f>+L14-L15</f>
+        <v>121.41787552643899</v>
       </c>
       <c r="X16" s="2">
         <f>+X14-X15</f>
@@ -2619,843 +2919,843 @@
       </c>
       <c r="AA16" s="2">
         <f t="shared" si="9"/>
-        <v>469.07760639587303</v>
+        <v>502.20000000000005</v>
       </c>
       <c r="AB16" s="2">
         <f>+AB14-AB15</f>
-        <v>483.14993458774916</v>
+        <v>492.15599999999978</v>
       </c>
       <c r="AC16" s="2">
         <f t="shared" ref="AC16:AJ16" si="15">+AC14-AC15</f>
-        <v>497.64443262538174</v>
+        <v>482.31287999999978</v>
       </c>
       <c r="AD16" s="2">
         <f t="shared" si="15"/>
-        <v>512.57376560414264</v>
+        <v>472.66662239999943</v>
       </c>
       <c r="AE16" s="2">
         <f t="shared" si="15"/>
-        <v>527.95097857226699</v>
+        <v>463.21328995199968</v>
       </c>
       <c r="AF16" s="2">
         <f t="shared" si="15"/>
-        <v>543.78950792943533</v>
+        <v>453.94902415295968</v>
       </c>
       <c r="AG16" s="2">
         <f t="shared" si="15"/>
-        <v>560.10319316731852</v>
+        <v>444.87004366990061</v>
       </c>
       <c r="AH16" s="2">
         <f t="shared" si="15"/>
-        <v>576.90628896233784</v>
+        <v>435.97264279650244</v>
       </c>
       <c r="AI16" s="2">
         <f t="shared" si="15"/>
-        <v>594.21347763120798</v>
+        <v>427.25318994057233</v>
       </c>
       <c r="AJ16" s="2">
         <f t="shared" si="15"/>
-        <v>612.03988196014416</v>
+        <v>418.70812614176106</v>
       </c>
       <c r="AK16" s="2">
         <f>+AJ16*(1+$AN$22)</f>
-        <v>618.16028077974556</v>
+        <v>422.89520740317869</v>
       </c>
       <c r="AL16" s="2">
         <f t="shared" ref="AL16:CW16" si="16">+AK16*(1+$AN$22)</f>
-        <v>624.34188358754307</v>
+        <v>427.12415947721047</v>
       </c>
       <c r="AM16" s="2">
         <f t="shared" si="16"/>
-        <v>630.58530242341851</v>
+        <v>431.39540107198258</v>
       </c>
       <c r="AN16" s="2">
         <f t="shared" si="16"/>
-        <v>636.89115544765275</v>
+        <v>435.70935508270242</v>
       </c>
       <c r="AO16" s="2">
         <f t="shared" si="16"/>
-        <v>643.26006700212929</v>
+        <v>440.06644863352943</v>
       </c>
       <c r="AP16" s="2">
         <f t="shared" si="16"/>
-        <v>649.69266767215061</v>
+        <v>444.46711311986473</v>
       </c>
       <c r="AQ16" s="2">
         <f t="shared" si="16"/>
-        <v>656.18959434887211</v>
+        <v>448.91178425106341</v>
       </c>
       <c r="AR16" s="2">
         <f t="shared" si="16"/>
-        <v>662.75149029236081</v>
+        <v>453.40090209357408</v>
       </c>
       <c r="AS16" s="2">
         <f t="shared" si="16"/>
-        <v>669.37900519528444</v>
+        <v>457.93491111450982</v>
       </c>
       <c r="AT16" s="2">
         <f t="shared" si="16"/>
-        <v>676.07279524723731</v>
+        <v>462.51426022565494</v>
       </c>
       <c r="AU16" s="2">
         <f t="shared" si="16"/>
-        <v>682.8335231997097</v>
+        <v>467.13940282791151</v>
       </c>
       <c r="AV16" s="2">
         <f t="shared" si="16"/>
-        <v>689.66185843170683</v>
+        <v>471.81079685619062</v>
       </c>
       <c r="AW16" s="2">
         <f t="shared" si="16"/>
-        <v>696.55847701602386</v>
+        <v>476.52890482475254</v>
       </c>
       <c r="AX16" s="2">
         <f t="shared" si="16"/>
-        <v>703.52406178618412</v>
+        <v>481.2941938730001</v>
       </c>
       <c r="AY16" s="2">
         <f t="shared" si="16"/>
-        <v>710.55930240404598</v>
+        <v>486.10713581173007</v>
       </c>
       <c r="AZ16" s="2">
         <f t="shared" si="16"/>
-        <v>717.66489542808642</v>
+        <v>490.9682071698474</v>
       </c>
       <c r="BA16" s="2">
         <f t="shared" si="16"/>
-        <v>724.84154438236726</v>
+        <v>495.87788924154586</v>
       </c>
       <c r="BB16" s="2">
         <f t="shared" si="16"/>
-        <v>732.08995982619092</v>
+        <v>500.83666813396133</v>
       </c>
       <c r="BC16" s="2">
         <f t="shared" si="16"/>
-        <v>739.41085942445284</v>
+        <v>505.84503481530095</v>
       </c>
       <c r="BD16" s="2">
         <f t="shared" si="16"/>
-        <v>746.80496801869742</v>
+        <v>510.90348516345398</v>
       </c>
       <c r="BE16" s="2">
         <f t="shared" si="16"/>
-        <v>754.27301769888436</v>
+        <v>516.01252001508851</v>
       </c>
       <c r="BF16" s="2">
         <f t="shared" si="16"/>
-        <v>761.81574787587317</v>
+        <v>521.17264521523941</v>
       </c>
       <c r="BG16" s="2">
         <f t="shared" si="16"/>
-        <v>769.43390535463186</v>
+        <v>526.38437166739186</v>
       </c>
       <c r="BH16" s="2">
         <f t="shared" si="16"/>
-        <v>777.12824440817815</v>
+        <v>531.64821538406579</v>
       </c>
       <c r="BI16" s="2">
         <f t="shared" si="16"/>
-        <v>784.8995268522599</v>
+        <v>536.96469753790643</v>
       </c>
       <c r="BJ16" s="2">
         <f t="shared" si="16"/>
-        <v>792.74852212078247</v>
+        <v>542.33434451328549</v>
       </c>
       <c r="BK16" s="2">
         <f t="shared" si="16"/>
-        <v>800.67600734199027</v>
+        <v>547.75768795841839</v>
       </c>
       <c r="BL16" s="2">
         <f t="shared" si="16"/>
-        <v>808.68276741541013</v>
+        <v>553.23526483800254</v>
       </c>
       <c r="BM16" s="2">
         <f t="shared" si="16"/>
-        <v>816.76959508956429</v>
+        <v>558.76761748638262</v>
       </c>
       <c r="BN16" s="2">
         <f t="shared" si="16"/>
-        <v>824.93729104045997</v>
+        <v>564.35529366124649</v>
       </c>
       <c r="BO16" s="2">
         <f t="shared" si="16"/>
-        <v>833.18666395086461</v>
+        <v>569.99884659785891</v>
       </c>
       <c r="BP16" s="2">
         <f t="shared" si="16"/>
-        <v>841.5185305903733</v>
+        <v>575.69883506383746</v>
       </c>
       <c r="BQ16" s="2">
         <f t="shared" si="16"/>
-        <v>849.93371589627702</v>
+        <v>581.45582341447584</v>
       </c>
       <c r="BR16" s="2">
         <f t="shared" si="16"/>
-        <v>858.43305305523984</v>
+        <v>587.27038164862063</v>
       </c>
       <c r="BS16" s="2">
         <f t="shared" si="16"/>
-        <v>867.01738358579223</v>
+        <v>593.14308546510688</v>
       </c>
       <c r="BT16" s="2">
         <f t="shared" si="16"/>
-        <v>875.68755742165013</v>
+        <v>599.074516319758</v>
       </c>
       <c r="BU16" s="2">
         <f t="shared" si="16"/>
-        <v>884.44443299586669</v>
+        <v>605.06526148295563</v>
       </c>
       <c r="BV16" s="2">
         <f t="shared" si="16"/>
-        <v>893.28887732582541</v>
+        <v>611.11591409778521</v>
       </c>
       <c r="BW16" s="2">
         <f t="shared" si="16"/>
-        <v>902.22176609908365</v>
+        <v>617.22707323876307</v>
       </c>
       <c r="BX16" s="2">
         <f t="shared" si="16"/>
-        <v>911.24398376007446</v>
+        <v>623.39934397115076</v>
       </c>
       <c r="BY16" s="2">
         <f t="shared" si="16"/>
-        <v>920.35642359767519</v>
+        <v>629.63333741086228</v>
       </c>
       <c r="BZ16" s="2">
         <f t="shared" si="16"/>
-        <v>929.55998783365192</v>
+        <v>635.92967078497088</v>
       </c>
       <c r="CA16" s="2">
         <f t="shared" si="16"/>
-        <v>938.85558771198839</v>
+        <v>642.28896749282057</v>
       </c>
       <c r="CB16" s="2">
         <f t="shared" si="16"/>
-        <v>948.24414358910826</v>
+        <v>648.7118571677488</v>
       </c>
       <c r="CC16" s="2">
         <f t="shared" si="16"/>
-        <v>957.72658502499939</v>
+        <v>655.19897573942626</v>
       </c>
       <c r="CD16" s="2">
         <f t="shared" si="16"/>
-        <v>967.3038508752494</v>
+        <v>661.75096549682053</v>
       </c>
       <c r="CE16" s="2">
         <f t="shared" si="16"/>
-        <v>976.97688938400188</v>
+        <v>668.36847515178874</v>
       </c>
       <c r="CF16" s="2">
         <f t="shared" si="16"/>
-        <v>986.7466582778419</v>
+        <v>675.05215990330669</v>
       </c>
       <c r="CG16" s="2">
         <f t="shared" si="16"/>
-        <v>996.61412486062034</v>
+        <v>681.80268150233974</v>
       </c>
       <c r="CH16" s="2">
         <f t="shared" si="16"/>
-        <v>1006.5802661092265</v>
+        <v>688.6207083173631</v>
       </c>
       <c r="CI16" s="2">
         <f t="shared" si="16"/>
-        <v>1016.6460687703187</v>
+        <v>695.50691540053674</v>
       </c>
       <c r="CJ16" s="2">
         <f t="shared" si="16"/>
-        <v>1026.812529458022</v>
+        <v>702.46198455454214</v>
       </c>
       <c r="CK16" s="2">
         <f t="shared" si="16"/>
-        <v>1037.0806547526022</v>
+        <v>709.48660440008757</v>
       </c>
       <c r="CL16" s="2">
         <f t="shared" si="16"/>
-        <v>1047.4514613001281</v>
+        <v>716.5814704440885</v>
       </c>
       <c r="CM16" s="2">
         <f t="shared" si="16"/>
-        <v>1057.9259759131294</v>
+        <v>723.74728514852939</v>
       </c>
       <c r="CN16" s="2">
         <f t="shared" si="16"/>
-        <v>1068.5052356722606</v>
+        <v>730.98475800001472</v>
       </c>
       <c r="CO16" s="2">
         <f t="shared" si="16"/>
-        <v>1079.1902880289831</v>
+        <v>738.29460558001483</v>
       </c>
       <c r="CP16" s="2">
         <f t="shared" si="16"/>
-        <v>1089.982190909273</v>
+        <v>745.67755163581501</v>
       </c>
       <c r="CQ16" s="2">
         <f t="shared" si="16"/>
-        <v>1100.8820128183656</v>
+        <v>753.13432715217311</v>
       </c>
       <c r="CR16" s="2">
         <f t="shared" si="16"/>
-        <v>1111.8908329465494</v>
+        <v>760.66567042369491</v>
       </c>
       <c r="CS16" s="2">
         <f t="shared" si="16"/>
-        <v>1123.0097412760149</v>
+        <v>768.27232712793182</v>
       </c>
       <c r="CT16" s="2">
         <f t="shared" si="16"/>
-        <v>1134.2398386887751</v>
+        <v>775.95505039921113</v>
       </c>
       <c r="CU16" s="2">
         <f t="shared" si="16"/>
-        <v>1145.5822370756628</v>
+        <v>783.71460090320329</v>
       </c>
       <c r="CV16" s="2">
         <f t="shared" si="16"/>
-        <v>1157.0380594464193</v>
+        <v>791.55174691223533</v>
       </c>
       <c r="CW16" s="2">
         <f t="shared" si="16"/>
-        <v>1168.6084400408836</v>
+        <v>799.46726438135772</v>
       </c>
       <c r="CX16" s="2">
         <f t="shared" ref="CX16:FC16" si="17">+CW16*(1+$AN$22)</f>
-        <v>1180.2945244412924</v>
+        <v>807.46193702517132</v>
       </c>
       <c r="CY16" s="2">
         <f t="shared" si="17"/>
-        <v>1192.0974696857054</v>
+        <v>815.53655639542308</v>
       </c>
       <c r="CZ16" s="2">
         <f t="shared" si="17"/>
-        <v>1204.0184443825624</v>
+        <v>823.69192195937728</v>
       </c>
       <c r="DA16" s="2">
         <f t="shared" si="17"/>
-        <v>1216.058628826388</v>
+        <v>831.92884117897108</v>
       </c>
       <c r="DB16" s="2">
         <f t="shared" si="17"/>
-        <v>1228.2192151146519</v>
+        <v>840.24812959076075</v>
       </c>
       <c r="DC16" s="2">
         <f t="shared" si="17"/>
-        <v>1240.5014072657984</v>
+        <v>848.65061088666835</v>
       </c>
       <c r="DD16" s="2">
         <f t="shared" si="17"/>
-        <v>1252.9064213384565</v>
+        <v>857.13711699553505</v>
       </c>
       <c r="DE16" s="2">
         <f t="shared" si="17"/>
-        <v>1265.4354855518411</v>
+        <v>865.70848816549039</v>
       </c>
       <c r="DF16" s="2">
         <f t="shared" si="17"/>
-        <v>1278.0898404073596</v>
+        <v>874.36557304714529</v>
       </c>
       <c r="DG16" s="2">
         <f t="shared" si="17"/>
-        <v>1290.8707388114333</v>
+        <v>883.10922877761675</v>
       </c>
       <c r="DH16" s="2">
         <f t="shared" si="17"/>
-        <v>1303.7794461995477</v>
+        <v>891.94032106539294</v>
       </c>
       <c r="DI16" s="2">
         <f t="shared" si="17"/>
-        <v>1316.8172406615431</v>
+        <v>900.8597242760469</v>
       </c>
       <c r="DJ16" s="2">
         <f t="shared" si="17"/>
-        <v>1329.9854130681586</v>
+        <v>909.86832151880742</v>
       </c>
       <c r="DK16" s="2">
         <f t="shared" si="17"/>
-        <v>1343.2852671988401</v>
+        <v>918.96700473399551</v>
       </c>
       <c r="DL16" s="2">
         <f t="shared" si="17"/>
-        <v>1356.7181198708286</v>
+        <v>928.15667478133548</v>
       </c>
       <c r="DM16" s="2">
         <f t="shared" si="17"/>
-        <v>1370.2853010695369</v>
+        <v>937.43824152914885</v>
       </c>
       <c r="DN16" s="2">
         <f t="shared" si="17"/>
-        <v>1383.9881540802323</v>
+        <v>946.81262394444036</v>
       </c>
       <c r="DO16" s="2">
         <f t="shared" si="17"/>
-        <v>1397.8280356210346</v>
+        <v>956.28075018388472</v>
       </c>
       <c r="DP16" s="2">
         <f t="shared" si="17"/>
-        <v>1411.806315977245</v>
+        <v>965.84355768572357</v>
       </c>
       <c r="DQ16" s="2">
         <f t="shared" si="17"/>
-        <v>1425.9243791370175</v>
+        <v>975.50199326258087</v>
       </c>
       <c r="DR16" s="2">
         <f t="shared" si="17"/>
-        <v>1440.1836229283876</v>
+        <v>985.2570131952067</v>
       </c>
       <c r="DS16" s="2">
         <f t="shared" si="17"/>
-        <v>1454.5854591576715</v>
+        <v>995.10958332715882</v>
       </c>
       <c r="DT16" s="2">
         <f t="shared" si="17"/>
-        <v>1469.1313137492482</v>
+        <v>1005.0606791604304</v>
       </c>
       <c r="DU16" s="2">
         <f t="shared" si="17"/>
-        <v>1483.8226268867406</v>
+        <v>1015.1112859520347</v>
       </c>
       <c r="DV16" s="2">
         <f t="shared" si="17"/>
-        <v>1498.660853155608</v>
+        <v>1025.2623988115549</v>
       </c>
       <c r="DW16" s="2">
         <f t="shared" si="17"/>
-        <v>1513.6474616871642</v>
+        <v>1035.5150227996705</v>
       </c>
       <c r="DX16" s="2">
         <f t="shared" si="17"/>
-        <v>1528.7839363040359</v>
+        <v>1045.8701730276673</v>
       </c>
       <c r="DY16" s="2">
         <f t="shared" si="17"/>
-        <v>1544.0717756670763</v>
+        <v>1056.328874757944</v>
       </c>
       <c r="DZ16" s="2">
         <f t="shared" si="17"/>
-        <v>1559.5124934237469</v>
+        <v>1066.8921635055235</v>
       </c>
       <c r="EA16" s="2">
         <f t="shared" si="17"/>
-        <v>1575.1076183579844</v>
+        <v>1077.5610851405788</v>
       </c>
       <c r="EB16" s="2">
         <f t="shared" si="17"/>
-        <v>1590.8586945415643</v>
+        <v>1088.3366959919847</v>
       </c>
       <c r="EC16" s="2">
         <f t="shared" si="17"/>
-        <v>1606.76728148698</v>
+        <v>1099.2200629519045</v>
       </c>
       <c r="ED16" s="2">
         <f t="shared" si="17"/>
-        <v>1622.8349543018498</v>
+        <v>1110.2122635814235</v>
       </c>
       <c r="EE16" s="2">
         <f t="shared" si="17"/>
-        <v>1639.0633038448684</v>
+        <v>1121.3143862172378</v>
       </c>
       <c r="EF16" s="2">
         <f t="shared" si="17"/>
-        <v>1655.4539368833171</v>
+        <v>1132.5275300794103</v>
       </c>
       <c r="EG16" s="2">
         <f t="shared" si="17"/>
-        <v>1672.0084762521503</v>
+        <v>1143.8528053802045</v>
       </c>
       <c r="EH16" s="2">
         <f t="shared" si="17"/>
-        <v>1688.7285610146719</v>
+        <v>1155.2913334340064</v>
       </c>
       <c r="EI16" s="2">
         <f t="shared" si="17"/>
-        <v>1705.6158466248187</v>
+        <v>1166.8442467683465</v>
       </c>
       <c r="EJ16" s="2">
         <f t="shared" si="17"/>
-        <v>1722.6720050910669</v>
+        <v>1178.5126892360299</v>
       </c>
       <c r="EK16" s="2">
         <f t="shared" si="17"/>
-        <v>1739.8987251419776</v>
+        <v>1190.2978161283902</v>
       </c>
       <c r="EL16" s="2">
         <f t="shared" si="17"/>
-        <v>1757.2977123933974</v>
+        <v>1202.2007942896741</v>
       </c>
       <c r="EM16" s="2">
         <f t="shared" si="17"/>
-        <v>1774.8706895173314</v>
+        <v>1214.222802232571</v>
       </c>
       <c r="EN16" s="2">
         <f t="shared" si="17"/>
-        <v>1792.6193964125048</v>
+        <v>1226.3650302548967</v>
       </c>
       <c r="EO16" s="2">
         <f t="shared" si="17"/>
-        <v>1810.5455903766299</v>
+        <v>1238.6286805574457</v>
       </c>
       <c r="EP16" s="2">
         <f t="shared" si="17"/>
-        <v>1828.6510462803963</v>
+        <v>1251.0149673630201</v>
       </c>
       <c r="EQ16" s="2">
         <f t="shared" si="17"/>
-        <v>1846.9375567432003</v>
+        <v>1263.5251170366503</v>
       </c>
       <c r="ER16" s="2">
         <f t="shared" si="17"/>
-        <v>1865.4069323106323</v>
+        <v>1276.1603682070167</v>
       </c>
       <c r="ES16" s="2">
         <f t="shared" si="17"/>
-        <v>1884.0610016337387</v>
+        <v>1288.921971889087</v>
       </c>
       <c r="ET16" s="2">
         <f t="shared" si="17"/>
-        <v>1902.9016116500761</v>
+        <v>1301.8111916079779</v>
       </c>
       <c r="EU16" s="2">
         <f t="shared" si="17"/>
-        <v>1921.9306277665769</v>
+        <v>1314.8293035240577</v>
       </c>
       <c r="EV16" s="2">
         <f t="shared" si="17"/>
-        <v>1941.1499340442426</v>
+        <v>1327.9775965592983</v>
       </c>
       <c r="EW16" s="2">
         <f t="shared" si="17"/>
-        <v>1960.561433384685</v>
+        <v>1341.2573725248913</v>
       </c>
       <c r="EX16" s="2">
         <f t="shared" si="17"/>
-        <v>1980.1670477185319</v>
+        <v>1354.6699462501401</v>
       </c>
       <c r="EY16" s="2">
         <f t="shared" si="17"/>
-        <v>1999.9687181957172</v>
+        <v>1368.2166457126416</v>
       </c>
       <c r="EZ16" s="2">
         <f t="shared" si="17"/>
-        <v>2019.9684053776743</v>
+        <v>1381.898812169768</v>
       </c>
       <c r="FA16" s="2">
         <f t="shared" si="17"/>
-        <v>2040.1680894314511</v>
+        <v>1395.7178002914657</v>
       </c>
       <c r="FB16" s="2">
         <f t="shared" si="17"/>
-        <v>2060.5697703257656</v>
+        <v>1409.6749782943803</v>
       </c>
       <c r="FC16" s="2">
         <f t="shared" si="17"/>
-        <v>2081.1754680290232</v>
+        <v>1423.771728077324</v>
       </c>
       <c r="FD16" s="2">
         <f t="shared" ref="FD16:GP16" si="18">+FC16*(1+$AN$22)</f>
-        <v>2101.9872227093133</v>
+        <v>1438.0094453580973</v>
       </c>
       <c r="FE16" s="2">
         <f t="shared" si="18"/>
-        <v>2123.0070949364062</v>
+        <v>1452.3895398116783</v>
       </c>
       <c r="FF16" s="2">
         <f t="shared" si="18"/>
-        <v>2144.2371658857705</v>
+        <v>1466.9134352097951</v>
       </c>
       <c r="FG16" s="2">
         <f t="shared" si="18"/>
-        <v>2165.6795375446281</v>
+        <v>1481.582569561893</v>
       </c>
       <c r="FH16" s="2">
         <f t="shared" si="18"/>
-        <v>2187.3363329200743</v>
+        <v>1496.398395257512</v>
       </c>
       <c r="FI16" s="2">
         <f t="shared" si="18"/>
-        <v>2209.2096962492751</v>
+        <v>1511.3623792100871</v>
       </c>
       <c r="FJ16" s="2">
         <f t="shared" si="18"/>
-        <v>2231.3017932117677</v>
+        <v>1526.476003002188</v>
       </c>
       <c r="FK16" s="2">
         <f t="shared" si="18"/>
-        <v>2253.6148111438856</v>
+        <v>1541.74076303221</v>
       </c>
       <c r="FL16" s="2">
         <f t="shared" si="18"/>
-        <v>2276.1509592553243</v>
+        <v>1557.158170662532</v>
       </c>
       <c r="FM16" s="2">
         <f t="shared" si="18"/>
-        <v>2298.9124688478778</v>
+        <v>1572.7297523691573</v>
       </c>
       <c r="FN16" s="2">
         <f t="shared" si="18"/>
-        <v>2321.9015935363568</v>
+        <v>1588.4570498928488</v>
       </c>
       <c r="FO16" s="2">
         <f t="shared" si="18"/>
-        <v>2345.1206094717204</v>
+        <v>1604.3416203917773</v>
       </c>
       <c r="FP16" s="2">
         <f t="shared" si="18"/>
-        <v>2368.5718155664376</v>
+        <v>1620.3850365956951</v>
       </c>
       <c r="FQ16" s="2">
         <f t="shared" si="18"/>
-        <v>2392.2575337221019</v>
+        <v>1636.588886961652</v>
       </c>
       <c r="FR16" s="2">
         <f t="shared" si="18"/>
-        <v>2416.1801090593231</v>
+        <v>1652.9547758312685</v>
       </c>
       <c r="FS16" s="2">
         <f t="shared" si="18"/>
-        <v>2440.3419101499162</v>
+        <v>1669.4843235895812</v>
       </c>
       <c r="FT16" s="2">
         <f t="shared" si="18"/>
-        <v>2464.7453292514156</v>
+        <v>1686.1791668254771</v>
       </c>
       <c r="FU16" s="2">
         <f t="shared" si="18"/>
-        <v>2489.3927825439296</v>
+        <v>1703.0409584937318</v>
       </c>
       <c r="FV16" s="2">
         <f t="shared" si="18"/>
-        <v>2514.2867103693688</v>
+        <v>1720.0713680786691</v>
       </c>
       <c r="FW16" s="2">
         <f t="shared" si="18"/>
-        <v>2539.4295774730626</v>
+        <v>1737.2720817594559</v>
       </c>
       <c r="FX16" s="2">
         <f t="shared" si="18"/>
-        <v>2564.8238732477935</v>
+        <v>1754.6448025770505</v>
       </c>
       <c r="FY16" s="2">
         <f t="shared" si="18"/>
-        <v>2590.4721119802716</v>
+        <v>1772.1912506028211</v>
       </c>
       <c r="FZ16" s="2">
         <f t="shared" si="18"/>
-        <v>2616.3768331000742</v>
+        <v>1789.9131631088494</v>
       </c>
       <c r="GA16" s="2">
         <f t="shared" si="18"/>
-        <v>2642.5406014310752</v>
+        <v>1807.8122947399379</v>
       </c>
       <c r="GB16" s="2">
         <f t="shared" si="18"/>
-        <v>2668.9660074453859</v>
+        <v>1825.8904176873373</v>
       </c>
       <c r="GC16" s="2">
         <f t="shared" si="18"/>
-        <v>2695.6556675198399</v>
+        <v>1844.1493218642106</v>
       </c>
       <c r="GD16" s="2">
         <f t="shared" si="18"/>
-        <v>2722.6122241950384</v>
+        <v>1862.5908150828527</v>
       </c>
       <c r="GE16" s="2">
         <f t="shared" si="18"/>
-        <v>2749.838346436989</v>
+        <v>1881.2167232336813</v>
       </c>
       <c r="GF16" s="2">
         <f t="shared" si="18"/>
-        <v>2777.3367299013589</v>
+        <v>1900.0288904660181</v>
       </c>
       <c r="GG16" s="2">
         <f t="shared" si="18"/>
-        <v>2805.1100972003724</v>
+        <v>1919.0291793706783</v>
       </c>
       <c r="GH16" s="2">
         <f t="shared" si="18"/>
-        <v>2833.1611981723763</v>
+        <v>1938.2194711643851</v>
       </c>
       <c r="GI16" s="2">
         <f t="shared" si="18"/>
-        <v>2861.4928101541</v>
+        <v>1957.6016658760291</v>
       </c>
       <c r="GJ16" s="2">
         <f t="shared" si="18"/>
-        <v>2890.1077382556409</v>
+        <v>1977.1776825347895</v>
       </c>
       <c r="GK16" s="2">
         <f t="shared" si="18"/>
-        <v>2919.0088156381976</v>
+        <v>1996.9494593601373</v>
       </c>
       <c r="GL16" s="2">
         <f t="shared" si="18"/>
-        <v>2948.1989037945796</v>
+        <v>2016.9189539537388</v>
       </c>
       <c r="GM16" s="2">
         <f t="shared" si="18"/>
-        <v>2977.6808928325254</v>
+        <v>2037.0881434932762</v>
       </c>
       <c r="GN16" s="2">
         <f t="shared" si="18"/>
-        <v>3007.4577017608508</v>
+        <v>2057.4590249282091</v>
       </c>
       <c r="GO16" s="2">
         <f t="shared" si="18"/>
-        <v>3037.5322787784594</v>
+        <v>2078.0336151774914</v>
       </c>
       <c r="GP16" s="2">
         <f t="shared" si="18"/>
-        <v>3067.907601566244</v>
+        <v>2098.8139513292663</v>
       </c>
       <c r="GQ16" s="2">
         <f t="shared" ref="GQ16:HX16" si="19">+GP16*(1+$AN$22)</f>
-        <v>3098.5866775819063</v>
+        <v>2119.8020908425588</v>
       </c>
       <c r="GR16" s="2">
         <f t="shared" si="19"/>
-        <v>3129.5725443577253</v>
+        <v>2141.0001117509842</v>
       </c>
       <c r="GS16" s="2">
         <f t="shared" si="19"/>
-        <v>3160.8682698013026</v>
+        <v>2162.4101128684938</v>
       </c>
       <c r="GT16" s="2">
         <f t="shared" si="19"/>
-        <v>3192.4769524993158</v>
+        <v>2184.0342139971785</v>
       </c>
       <c r="GU16" s="2">
         <f t="shared" si="19"/>
-        <v>3224.401722024309</v>
+        <v>2205.8745561371502</v>
       </c>
       <c r="GV16" s="2">
         <f t="shared" si="19"/>
-        <v>3256.6457392445523</v>
+        <v>2227.9333016985215</v>
       </c>
       <c r="GW16" s="2">
         <f t="shared" si="19"/>
-        <v>3289.2121966369978</v>
+        <v>2250.2126347155067</v>
       </c>
       <c r="GX16" s="2">
         <f t="shared" si="19"/>
-        <v>3322.1043186033676</v>
+        <v>2272.7147610626616</v>
       </c>
       <c r="GY16" s="2">
         <f t="shared" si="19"/>
-        <v>3355.3253617894011</v>
+        <v>2295.4419086732883</v>
       </c>
       <c r="GZ16" s="2">
         <f t="shared" si="19"/>
-        <v>3388.878615407295</v>
+        <v>2318.396327760021</v>
       </c>
       <c r="HA16" s="2">
         <f t="shared" si="19"/>
-        <v>3422.7674015613679</v>
+        <v>2341.580291037621</v>
       </c>
       <c r="HB16" s="2">
         <f t="shared" si="19"/>
-        <v>3456.9950755769814</v>
+        <v>2364.9960939479975</v>
       </c>
       <c r="HC16" s="2">
         <f t="shared" si="19"/>
-        <v>3491.5650263327511</v>
+        <v>2388.6460548874775</v>
       </c>
       <c r="HD16" s="2">
         <f t="shared" si="19"/>
-        <v>3526.4806765960789</v>
+        <v>2412.5325154363522</v>
       </c>
       <c r="HE16" s="2">
         <f t="shared" si="19"/>
-        <v>3561.7454833620395</v>
+        <v>2436.6578405907158</v>
       </c>
       <c r="HF16" s="2">
         <f t="shared" si="19"/>
-        <v>3597.3629381956598</v>
+        <v>2461.0244189966229</v>
       </c>
       <c r="HG16" s="2">
         <f t="shared" si="19"/>
-        <v>3633.3365675776163</v>
+        <v>2485.634663186589</v>
       </c>
       <c r="HH16" s="2">
         <f t="shared" si="19"/>
-        <v>3669.6699332533926</v>
+        <v>2510.491009818455</v>
       </c>
       <c r="HI16" s="2">
         <f t="shared" si="19"/>
-        <v>3706.3666325859267</v>
+        <v>2535.5959199166396</v>
       </c>
       <c r="HJ16" s="2">
         <f t="shared" si="19"/>
-        <v>3743.4302989117859</v>
+        <v>2560.9518791158062</v>
       </c>
       <c r="HK16" s="2">
         <f t="shared" si="19"/>
-        <v>3780.8646019009038</v>
+        <v>2586.5613979069644</v>
       </c>
       <c r="HL16" s="2">
         <f t="shared" si="19"/>
-        <v>3818.6732479199127</v>
+        <v>2612.4270118860341</v>
       </c>
       <c r="HM16" s="2">
         <f t="shared" si="19"/>
-        <v>3856.8599803991119</v>
+        <v>2638.5512820048943</v>
       </c>
       <c r="HN16" s="2">
         <f t="shared" si="19"/>
-        <v>3895.4285802031031</v>
+        <v>2664.9367948249433</v>
       </c>
       <c r="HO16" s="2">
         <f t="shared" si="19"/>
-        <v>3934.382866005134</v>
+        <v>2691.5861627731929</v>
       </c>
       <c r="HP16" s="2">
         <f t="shared" si="19"/>
-        <v>3973.7266946651853</v>
+        <v>2718.5020244009247</v>
       </c>
       <c r="HQ16" s="2">
         <f t="shared" si="19"/>
-        <v>4013.463961611837</v>
+        <v>2745.6870446449338</v>
       </c>
       <c r="HR16" s="2">
         <f t="shared" si="19"/>
-        <v>4053.5986012279554</v>
+        <v>2773.1439150913834</v>
       </c>
       <c r="HS16" s="2">
         <f t="shared" si="19"/>
-        <v>4094.1345872402349</v>
+        <v>2800.8753542422974</v>
       </c>
       <c r="HT16" s="2">
         <f t="shared" si="19"/>
-        <v>4135.0759331126374</v>
+        <v>2828.8841077847205</v>
       </c>
       <c r="HU16" s="2">
         <f t="shared" si="19"/>
-        <v>4176.4266924437634</v>
+        <v>2857.1729488625679</v>
       </c>
       <c r="HV16" s="2">
         <f t="shared" si="19"/>
-        <v>4218.1909593682012</v>
+        <v>2885.7446783511937</v>
       </c>
       <c r="HW16" s="2">
         <f t="shared" si="19"/>
-        <v>4260.3728689618829</v>
+        <v>2914.6021251347056</v>
       </c>
       <c r="HX16" s="2">
         <f t="shared" si="19"/>
-        <v>4302.9765976515018</v>
+        <v>2943.7481463860527</v>
       </c>
       <c r="HY16" s="2">
-        <f t="shared" ref="HY16:ID16" si="20">+HX16*(1+$AN$22)</f>
-        <v>4346.0063636280165</v>
+        <f t="shared" ref="HY16:IB16" si="20">+HX16*(1+$AN$22)</f>
+        <v>2973.1856278499131</v>
       </c>
       <c r="HZ16" s="2">
         <f t="shared" si="20"/>
-        <v>4389.4664272642967</v>
+        <v>3002.9174841284121</v>
       </c>
       <c r="IA16" s="2">
         <f t="shared" si="20"/>
-        <v>4433.36109153694</v>
+        <v>3032.9466589696963</v>
       </c>
       <c r="IB16" s="2">
         <f t="shared" si="20"/>
-        <v>4477.6947024523097</v>
+        <v>3063.2761255593932</v>
       </c>
       <c r="XFD16" s="2">
         <f t="shared" ref="XFD16" si="21">+XFC16*(1+$AN$22)</f>
@@ -3476,219 +3776,288 @@
       <c r="B20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="5">
-        <f>+C8/C6</f>
+      <c r="C20" s="16">
+        <f t="shared" ref="C20:J20" si="22">+C8/C6</f>
         <v>0.42163961714523512</v>
       </c>
-      <c r="D20" s="5">
-        <f>+D8/D6</f>
+      <c r="D20" s="16">
+        <f t="shared" si="22"/>
         <v>0.40181644359464624</v>
       </c>
-      <c r="E20" s="5">
-        <f>+E8/E6</f>
+      <c r="E20" s="16">
+        <f t="shared" si="22"/>
         <v>0.40209828823854227</v>
       </c>
-      <c r="F20" s="5">
-        <f>+F8/F6</f>
+      <c r="F20" s="16">
+        <f t="shared" si="22"/>
         <v>0.41931707317073186</v>
       </c>
-      <c r="G20" s="5">
-        <f>+G8/G6</f>
+      <c r="G20" s="16">
+        <f t="shared" si="22"/>
         <v>0.41357042583060361</v>
       </c>
-      <c r="H20" s="5">
-        <f>+H8/H6</f>
+      <c r="H20" s="16">
+        <f t="shared" si="22"/>
         <v>0.4108266890474192</v>
       </c>
-      <c r="I20" s="5">
-        <f>+I8/I6</f>
+      <c r="I20" s="16">
+        <f t="shared" si="22"/>
         <v>0.41554404145077722</v>
       </c>
-      <c r="J20" s="5">
-        <f>+J8/J6</f>
-        <v>0.41331371877626683</v>
-      </c>
+      <c r="J20" s="16">
+        <f t="shared" si="22"/>
+        <v>0.40683512088711143</v>
+      </c>
+      <c r="K20" s="16">
+        <f t="shared" ref="K20" si="23">+K8/K6</f>
+        <v>0.4125941665056983</v>
+      </c>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
       <c r="X20" s="5">
         <f>+X8/X6</f>
         <v>0.47476073284112663</v>
       </c>
       <c r="Y20" s="5">
-        <f t="shared" ref="Y20:AJ20" si="22">+Y8/Y6</f>
+        <f t="shared" ref="Y20:AJ20" si="24">+Y8/Y6</f>
         <v>0.44155980219596008</v>
       </c>
       <c r="Z20" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.41187170895165154</v>
       </c>
       <c r="AA20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043278</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465099</v>
       </c>
       <c r="AB20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043278</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465093</v>
       </c>
       <c r="AC20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043278</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465088</v>
       </c>
       <c r="AD20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043267</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465082</v>
       </c>
       <c r="AE20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043267</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465093</v>
       </c>
       <c r="AF20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043272</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465088</v>
       </c>
       <c r="AG20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043278</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465093</v>
       </c>
       <c r="AH20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043272</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465088</v>
       </c>
       <c r="AI20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043267</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465082</v>
       </c>
       <c r="AJ20" s="5">
-        <f t="shared" si="22"/>
-        <v>0.41332769187043272</v>
+        <f t="shared" si="24"/>
+        <v>0.41158335168465088</v>
       </c>
     </row>
     <row r="21" spans="2:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="16">
         <f>+C15/C14</f>
         <v>7.6091010816859372E-2</v>
       </c>
-      <c r="D21" s="5">
-        <f t="shared" ref="D21:J21" si="23">+D15/D14</f>
+      <c r="D21" s="16">
+        <f t="shared" ref="D21:J21" si="25">+D15/D14</f>
         <v>4.8236514522821586E-2</v>
       </c>
-      <c r="E21" s="5">
-        <f t="shared" si="23"/>
+      <c r="E21" s="16">
+        <f t="shared" si="25"/>
         <v>9.2455621301775121E-2</v>
       </c>
-      <c r="F21" s="5">
-        <f t="shared" si="23"/>
+      <c r="F21" s="16">
+        <f t="shared" si="25"/>
         <v>-9.4142259414226083E-3</v>
       </c>
-      <c r="G21" s="5">
-        <f t="shared" si="23"/>
+      <c r="G21" s="16">
+        <f t="shared" si="25"/>
         <v>0.14776274713839752</v>
       </c>
-      <c r="H21" s="5">
-        <f t="shared" si="23"/>
+      <c r="H21" s="16">
+        <f t="shared" si="25"/>
         <v>0.27577741407528639</v>
       </c>
-      <c r="I21" s="5">
-        <f t="shared" si="23"/>
+      <c r="I21" s="16">
+        <f t="shared" si="25"/>
         <v>6.1565523306948103E-2</v>
       </c>
-      <c r="J21" s="5">
-        <f t="shared" si="23"/>
-        <v>6.1565523306948103E-2</v>
-      </c>
-      <c r="X21" s="4" t="e">
-        <f t="shared" ref="X21:AJ22" si="24">+X10/X5</f>
-        <v>#DIV/0!</v>
+      <c r="J21" s="16">
+        <f t="shared" si="25"/>
+        <v>-0.15670436187399028</v>
+      </c>
+      <c r="K21" s="16">
+        <f t="shared" ref="K21" si="26">+K15/K14</f>
+        <v>0.25144270403957125</v>
+      </c>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="X21" s="16">
+        <f t="shared" ref="X21:AJ21" si="27">+X15/X14</f>
+        <v>0.12538911717096252</v>
+      </c>
+      <c r="Y21" s="16">
+        <f t="shared" si="27"/>
+        <v>8.4188371481189184E-2</v>
+      </c>
+      <c r="Z21" s="16">
+        <f t="shared" si="27"/>
+        <v>5.131461958592657E-2</v>
+      </c>
+      <c r="AA21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AB21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AC21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AD21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AE21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AF21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AG21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AH21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AI21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AJ21" s="16">
+        <f t="shared" si="27"/>
+        <v>9.0052545751041838E-2</v>
+      </c>
+      <c r="AM21" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="13">
         <f>+C11/C6</f>
         <v>0.22863087806908036</v>
       </c>
-      <c r="D22" s="4">
-        <f t="shared" ref="D22:J22" si="25">+D11/D6</f>
+      <c r="D22" s="13">
+        <f t="shared" ref="D22:J22" si="28">+D11/D6</f>
         <v>0.1807839388145315</v>
       </c>
-      <c r="E22" s="4">
-        <f t="shared" si="25"/>
+      <c r="E22" s="13">
+        <f t="shared" si="28"/>
         <v>0.14599668691330761</v>
       </c>
-      <c r="F22" s="4">
-        <f t="shared" si="25"/>
+      <c r="F22" s="13">
+        <f t="shared" si="28"/>
         <v>0.18760975609756114</v>
       </c>
-      <c r="G22" s="4">
-        <f t="shared" si="25"/>
+      <c r="G22" s="13">
+        <f t="shared" si="28"/>
         <v>0.17117454375292465</v>
       </c>
-      <c r="H22" s="4">
-        <f t="shared" si="25"/>
+      <c r="H22" s="13">
+        <f t="shared" si="28"/>
         <v>0.12284934955937896</v>
       </c>
-      <c r="I22" s="4">
-        <f t="shared" si="25"/>
+      <c r="I22" s="13">
+        <f t="shared" si="28"/>
         <v>0.11637305699481866</v>
       </c>
-      <c r="J22" s="4">
-        <f t="shared" si="25"/>
-        <v>0.11414273432030823</v>
+      <c r="J22" s="13">
+        <f t="shared" si="28"/>
+        <v>0.10252681330667152</v>
+      </c>
+      <c r="K22" s="13">
+        <f t="shared" ref="K22" si="29">+K11/K6</f>
+        <v>0.11145451033417039</v>
       </c>
       <c r="X22" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="X22:AJ22" si="30">+X11/X6</f>
         <v>0.30199617172545806</v>
       </c>
       <c r="Y22" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.24861704802615034</v>
       </c>
       <c r="Z22" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.1886787936811872</v>
       </c>
       <c r="AA22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.13198262621763571</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573763</v>
       </c>
       <c r="AB22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.13198262621763571</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573754</v>
       </c>
       <c r="AC22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.13198262621763571</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573754</v>
       </c>
       <c r="AD22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.1319826262176356</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573746</v>
       </c>
       <c r="AE22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.1319826262176356</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573754</v>
       </c>
       <c r="AF22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.13198262621763568</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573754</v>
       </c>
       <c r="AG22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.13198262621763571</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573757</v>
       </c>
       <c r="AH22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.13198262621763565</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573751</v>
       </c>
       <c r="AI22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.13198262621763562</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573749</v>
       </c>
       <c r="AJ22" s="4">
-        <f t="shared" si="24"/>
-        <v>0.13198262621763562</v>
+        <f t="shared" si="30"/>
+        <v>0.12848369179573754</v>
       </c>
       <c r="AM22" s="2" t="s">
         <v>40</v>
@@ -3698,7 +4067,7 @@
       </c>
     </row>
     <row r="23" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="19" t="s">
         <v>35</v>
       </c>
       <c r="AM23" s="2" t="s">
@@ -3712,18 +4081,36 @@
       <c r="B24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="5">
-        <f>+G6/C6-1</f>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="16">
+        <f t="shared" ref="G24:L26" si="31">+G6/C6-1</f>
         <v>-0.11069496462754891</v>
       </c>
-      <c r="H24" s="5">
-        <f>+H6/D6-1</f>
+      <c r="H24" s="16">
+        <f t="shared" si="31"/>
         <v>-8.8718929254302026E-2</v>
       </c>
-      <c r="I24" s="5">
-        <f>+I6/E6-1</f>
+      <c r="I24" s="16">
+        <f t="shared" si="31"/>
         <v>6.5709552733296483E-2</v>
       </c>
+      <c r="J24" s="16">
+        <f t="shared" si="31"/>
+        <v>7.3365853658536651E-2</v>
+      </c>
+      <c r="K24" s="16">
+        <f t="shared" si="31"/>
+        <v>-3.0978006551239945E-2</v>
+      </c>
+      <c r="L24" s="16">
+        <f t="shared" si="31"/>
+        <v>-5.5812001678556489E-2</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
       <c r="Y24" s="4">
         <f>+Y6/X6-1</f>
         <v>-0.12999726551818436</v>
@@ -3734,68 +4121,83 @@
       </c>
       <c r="AA24" s="4">
         <f>+AA6/Z6-1</f>
-        <v>-4.2197223551938778E-2</v>
+        <v>-2.1804691239827756E-2</v>
       </c>
       <c r="AB24" s="4">
-        <f t="shared" ref="AB24:AJ24" si="26">+AB6/AA6-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f>+AB6/AA6-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AC24" s="4">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000027E-2</v>
+        <f>+AC6/AB6-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AD24" s="4">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000027E-2</v>
+        <f>+AD6/AC6-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AE24" s="4">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000027E-2</v>
+        <f>+AE6/AD6-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AF24" s="4">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000027E-2</v>
+        <f>+AF6/AE6-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AG24" s="4">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000027E-2</v>
+        <f>+AG6/AF6-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AH24" s="4">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000027E-2</v>
+        <f>+AH6/AG6-1</f>
+        <v>-1.9999999999999907E-2</v>
       </c>
       <c r="AI24" s="4">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AB24:AJ24" si="32">+AI6/AH6-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AJ24" s="4">
-        <f t="shared" si="26"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="32"/>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AM24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AN24" s="10">
+      <c r="AN24" s="9">
         <f>NPV(AN23,AA16:IB16)</f>
-        <v>10805.275296603559</v>
+        <v>8135.9450964679827</v>
       </c>
     </row>
     <row r="25" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="5">
-        <f>+G7/C7-1</f>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="16">
+        <f t="shared" si="31"/>
         <v>-9.8287523384659625E-2</v>
       </c>
-      <c r="H25" s="5">
-        <f>+H7/D7-1</f>
+      <c r="H25" s="16">
+        <f t="shared" si="31"/>
         <v>-0.10244526130733578</v>
       </c>
-      <c r="I25" s="5">
-        <f>+I7/E7-1</f>
+      <c r="I25" s="16">
+        <f t="shared" si="31"/>
         <v>4.1743627632065072E-2</v>
       </c>
+      <c r="J25" s="16">
+        <f t="shared" si="31"/>
+        <v>9.6438172043011194E-2</v>
+      </c>
+      <c r="K25" s="16">
+        <f t="shared" si="31"/>
+        <v>-2.9364826045323977E-2</v>
+      </c>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
       <c r="Y25" s="4">
         <f>+Y7/X7-1</f>
         <v>-7.5003470776065506E-2</v>
@@ -3804,30 +4206,77 @@
         <f>+Z7/Y7-1</f>
         <v>-7.8008329893812678E-2</v>
       </c>
+      <c r="AA25" s="4">
+        <f>+AA7/Z7-1</f>
+        <v>-2.1325085463128612E-2</v>
+      </c>
+      <c r="AB25" s="4">
+        <f>+AB7/AA7-1</f>
+        <v>-2.000000000000024E-2</v>
+      </c>
+      <c r="AC25" s="4">
+        <f>+AC7/AB7-1</f>
+        <v>-1.9999999999999907E-2</v>
+      </c>
+      <c r="AD25" s="4">
+        <f>+AD7/AC7-1</f>
+        <v>-1.9999999999999907E-2</v>
+      </c>
+      <c r="AE25" s="4">
+        <f>+AE7/AD7-1</f>
+        <v>-2.0000000000000129E-2</v>
+      </c>
+      <c r="AF25" s="4">
+        <f>+AF7/AE7-1</f>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="AG25" s="4">
+        <f>+AG7/AF7-1</f>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="AH25" s="4">
+        <f>+AH7/AG7-1</f>
+        <v>-1.9999999999999907E-2</v>
+      </c>
       <c r="AM25" s="4" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AN25" s="1">
         <f>+Main!F4</f>
-        <v>148.42756800000001</v>
+        <v>150.37361200000001</v>
       </c>
     </row>
     <row r="26" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="5">
-        <f>+G8/C8-1</f>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="16">
+        <f t="shared" si="31"/>
         <v>-0.12771417291748921</v>
       </c>
-      <c r="H26" s="5">
-        <f>+H8/D8-1</f>
+      <c r="H26" s="16">
+        <f t="shared" si="31"/>
         <v>-6.8284558648584182E-2</v>
       </c>
-      <c r="I26" s="5">
-        <f>+I8/E8-1</f>
+      <c r="I26" s="16">
+        <f t="shared" si="31"/>
         <v>0.10134578412524031</v>
       </c>
+      <c r="J26" s="16">
+        <f t="shared" si="31"/>
+        <v>4.141461144718428E-2</v>
+      </c>
+      <c r="K26" s="16">
+        <f t="shared" si="31"/>
+        <v>-3.3265444670739885E-2</v>
+      </c>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
       <c r="Y26" s="4">
         <f>+Y8/X8-1</f>
         <v>-0.19083822908267112</v>
@@ -3836,12 +4285,44 @@
         <f>+Z8/Y8-1</f>
         <v>-0.18341005077587413</v>
       </c>
-      <c r="AM26" s="8" t="s">
+      <c r="AA26" s="4">
+        <f>+AA8/Z8-1</f>
+        <v>-2.2489539748954179E-2</v>
+      </c>
+      <c r="AB26" s="4">
+        <f>+AB8/AA8-1</f>
+        <v>-2.0000000000000129E-2</v>
+      </c>
+      <c r="AC26" s="4">
+        <f>+AC8/AB8-1</f>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="AD26" s="4">
+        <f>+AD8/AC8-1</f>
+        <v>-2.0000000000000129E-2</v>
+      </c>
+      <c r="AE26" s="4">
+        <f>+AE8/AD8-1</f>
+        <v>-1.9999999999999796E-2</v>
+      </c>
+      <c r="AF26" s="4">
+        <f>+AF8/AE8-1</f>
+        <v>-2.0000000000000129E-2</v>
+      </c>
+      <c r="AG26" s="4">
+        <f>+AG8/AF8-1</f>
+        <v>-1.9999999999999907E-2</v>
+      </c>
+      <c r="AH26" s="4">
+        <f>+AH8/AG8-1</f>
+        <v>-2.0000000000000129E-2</v>
+      </c>
+      <c r="AM26" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AN26" s="9">
+      <c r="AN26" s="8">
         <f>+AN24/AN25</f>
-        <v>72.798304534664055</v>
+        <v>54.104872445758517</v>
       </c>
     </row>
     <row r="27" spans="2:40" x14ac:dyDescent="0.2">
@@ -3856,183 +4337,853 @@
     <row r="28" spans="2:40" x14ac:dyDescent="0.2">
       <c r="AN28" s="4">
         <f>+AN26/AN27-1</f>
-        <v>-2.2972694475049682E-2</v>
+        <v>-0.27385757018174051</v>
       </c>
     </row>
     <row r="29" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C29" s="4">
-        <f t="shared" ref="C29:I29" si="27">+C9/C$6</f>
+      <c r="C29" s="13">
+        <f t="shared" ref="C29:H29" si="33">+C9/C$6</f>
         <v>0.12742405326674988</v>
       </c>
-      <c r="D29" s="4">
-        <f t="shared" si="27"/>
+      <c r="D29" s="13">
+        <f t="shared" si="33"/>
         <v>0.14760994263862334</v>
       </c>
-      <c r="E29" s="4">
-        <f t="shared" si="27"/>
+      <c r="E29" s="13">
+        <f t="shared" si="33"/>
         <v>0.17747101049144118</v>
       </c>
-      <c r="F29" s="4">
-        <f t="shared" si="27"/>
+      <c r="F29" s="13">
+        <f t="shared" si="33"/>
         <v>0.15951219512195128</v>
       </c>
-      <c r="G29" s="4">
-        <f t="shared" si="27"/>
+      <c r="G29" s="13">
+        <f t="shared" si="33"/>
         <v>0.16509124941506786</v>
       </c>
-      <c r="H29" s="4">
-        <f t="shared" si="27"/>
+      <c r="H29" s="13">
+        <f t="shared" si="33"/>
         <v>0.19565673520772134</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="13">
         <f>+I9/I$6</f>
         <v>0.20663212435233161</v>
       </c>
-      <c r="J29" s="4">
+      <c r="J29" s="13">
         <f>+J9/J$6</f>
-        <v>0.20663212435233161</v>
-      </c>
+        <v>0.20278131248863843</v>
+      </c>
+      <c r="K29" s="13">
+        <f>+K9/K$6</f>
+        <v>0.19644581804133668</v>
+      </c>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
       <c r="X29" s="4">
-        <f>+X9/X$6</f>
+        <f t="shared" ref="X29:AB30" si="34">+X9/X$6</f>
         <v>0.11264242092790082</v>
       </c>
       <c r="Y29" s="4">
-        <f>+Y9/Y$6</f>
+        <f t="shared" si="34"/>
         <v>0.12714776632302405</v>
       </c>
       <c r="Z29" s="4">
-        <f>+Z9/Z$6</f>
+        <f t="shared" si="34"/>
         <v>0.15119674485399714</v>
       </c>
       <c r="AA29" s="4">
-        <f>+AA9/AA$6</f>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="34"/>
+        <v>0.19217499816486824</v>
       </c>
       <c r="AB29" s="4">
-        <f>+AB9/AB$6</f>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="34"/>
+        <v>0.19217499816486824</v>
       </c>
       <c r="AC29" s="4">
-        <f t="shared" ref="AC29:AJ29" si="28">+AC9/AC$6</f>
-        <v>0.19292590804348569</v>
+        <f t="shared" ref="AC29:AJ29" si="35">+AC9/AC$6</f>
+        <v>0.19217499816486824</v>
       </c>
       <c r="AD29" s="4">
-        <f t="shared" si="28"/>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="35"/>
+        <v>0.19217499816486824</v>
       </c>
       <c r="AE29" s="4">
-        <f t="shared" si="28"/>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="35"/>
+        <v>0.19217499816486824</v>
       </c>
       <c r="AF29" s="4">
-        <f t="shared" si="28"/>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="35"/>
+        <v>0.19217499816486824</v>
       </c>
       <c r="AG29" s="4">
-        <f t="shared" si="28"/>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="35"/>
+        <v>0.19217499816486822</v>
       </c>
       <c r="AH29" s="4">
-        <f t="shared" si="28"/>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="35"/>
+        <v>0.19217499816486822</v>
       </c>
       <c r="AI29" s="4">
-        <f t="shared" si="28"/>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="35"/>
+        <v>0.19217499816486822</v>
       </c>
       <c r="AJ29" s="4">
-        <f t="shared" si="28"/>
-        <v>0.19292590804348569</v>
+        <f t="shared" si="35"/>
+        <v>0.19217499816486822</v>
       </c>
     </row>
     <row r="30" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C30" s="4">
-        <f t="shared" ref="C30:I30" si="29">+C10/C$6</f>
+      <c r="C30" s="13">
+        <f t="shared" ref="C30:H30" si="36">+C10/C$6</f>
         <v>6.5584685809404908E-2</v>
       </c>
-      <c r="D30" s="4">
-        <f t="shared" si="29"/>
+      <c r="D30" s="13">
+        <f t="shared" si="36"/>
         <v>7.3422562141491399E-2</v>
       </c>
-      <c r="E30" s="4">
-        <f t="shared" si="29"/>
+      <c r="E30" s="13">
+        <f t="shared" si="36"/>
         <v>7.8630590833793493E-2</v>
       </c>
-      <c r="F30" s="4">
-        <f t="shared" si="29"/>
+      <c r="F30" s="13">
+        <f t="shared" si="36"/>
         <v>7.2195121951219507E-2</v>
       </c>
-      <c r="G30" s="4">
-        <f t="shared" si="29"/>
+      <c r="G30" s="13">
+        <f t="shared" si="36"/>
         <v>7.7304632662611131E-2</v>
       </c>
-      <c r="H30" s="4">
-        <f t="shared" si="29"/>
+      <c r="H30" s="13">
+        <f t="shared" si="36"/>
         <v>9.2320604280318921E-2</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="13">
         <f>+I10/I$6</f>
         <v>9.2538860103626941E-2</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="13">
         <f>+J10/J$6</f>
-        <v>9.2538860103626941E-2</v>
-      </c>
+        <v>0.10152699509180149</v>
+      </c>
+      <c r="K30" s="13">
+        <f>+K10/K$6</f>
+        <v>0.10469383813019123</v>
+      </c>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
       <c r="X30" s="4">
-        <f>+X10/X$6</f>
+        <f t="shared" si="34"/>
         <v>6.012214018776775E-2</v>
       </c>
       <c r="Y30" s="4">
-        <f>+Y10/Y$6</f>
+        <f t="shared" si="34"/>
         <v>6.5794987846785682E-2</v>
       </c>
       <c r="Z30" s="4">
-        <f>+Z10/Z$6</f>
+        <f t="shared" si="34"/>
         <v>7.1996170416467206E-2</v>
       </c>
       <c r="AA30" s="4">
-        <f>+AA10/AA$6</f>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="34"/>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AB30" s="4">
-        <f>+AB10/AB$6</f>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="34"/>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AC30" s="4">
-        <f t="shared" ref="AC30:AJ30" si="30">+AC10/AC$6</f>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" ref="AC30:AJ30" si="37">+AC10/AC$6</f>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AD30" s="4">
-        <f t="shared" si="30"/>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="37"/>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AE30" s="4">
-        <f t="shared" si="30"/>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="37"/>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AF30" s="4">
-        <f t="shared" si="30"/>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="37"/>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AG30" s="4">
-        <f t="shared" si="30"/>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="37"/>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AH30" s="4">
-        <f t="shared" si="30"/>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="37"/>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AI30" s="4">
-        <f t="shared" si="30"/>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="37"/>
+        <v>9.0924661724045119E-2</v>
       </c>
       <c r="AJ30" s="4">
-        <f t="shared" si="30"/>
-        <v>8.8419157609311377E-2</v>
+        <f t="shared" si="37"/>
+        <v>9.0924661724045119E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+    </row>
+    <row r="32" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="15">
+        <f>+F33-F43</f>
+        <v>579.79999999999995</v>
+      </c>
+      <c r="G32" s="15">
+        <f>+G33-G43</f>
+        <v>760.09999999999991</v>
+      </c>
+      <c r="H32" s="15">
+        <f>+H33-H43</f>
+        <v>532.6</v>
+      </c>
+      <c r="I32" s="15">
+        <f>+I33-I43</f>
+        <v>341.30000000000007</v>
+      </c>
+      <c r="J32" s="15">
+        <f>+J33-J43</f>
+        <v>392.60000000000014</v>
+      </c>
+      <c r="K32" s="15">
+        <f>+K33-K43</f>
+        <v>572.39999999999986</v>
+      </c>
+      <c r="AA32" s="2">
+        <f>+K32</f>
+        <v>572.39999999999986</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="21">
+        <v>1574.1</v>
+      </c>
+      <c r="G33" s="21">
+        <v>1754.8</v>
+      </c>
+      <c r="H33" s="21">
+        <v>1527.7</v>
+      </c>
+      <c r="I33" s="21">
+        <v>1336.7</v>
+      </c>
+      <c r="J33" s="21">
+        <v>1388.4</v>
+      </c>
+      <c r="K33" s="21">
+        <v>1568.6</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="15">
+        <v>508.8</v>
+      </c>
+      <c r="G34" s="15">
+        <v>520</v>
+      </c>
+      <c r="H34" s="15">
+        <v>371.9</v>
+      </c>
+      <c r="I34" s="15">
+        <v>396.2</v>
+      </c>
+      <c r="J34" s="15">
+        <v>598.1</v>
+      </c>
+      <c r="K34" s="15">
+        <v>398.4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" s="15">
+        <v>784.8</v>
+      </c>
+      <c r="G35" s="15">
+        <v>699.7</v>
+      </c>
+      <c r="H35" s="15">
+        <v>678.3</v>
+      </c>
+      <c r="I35" s="15">
+        <v>706.5</v>
+      </c>
+      <c r="J35" s="15">
+        <v>754.7</v>
+      </c>
+      <c r="K35" s="15">
+        <v>767.5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" s="15">
+        <v>1280.3</v>
+      </c>
+      <c r="G36" s="15">
+        <v>1247</v>
+      </c>
+      <c r="H36" s="15">
+        <v>1231.7</v>
+      </c>
+      <c r="I36" s="15">
+        <v>1213.8</v>
+      </c>
+      <c r="J36" s="15">
+        <v>1194.5999999999999</v>
+      </c>
+      <c r="K36" s="15">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="15">
+        <v>3077.2</v>
+      </c>
+      <c r="G37" s="15">
+        <v>3060.7</v>
+      </c>
+      <c r="H37" s="15">
+        <v>3015.5</v>
+      </c>
+      <c r="I37" s="15">
+        <v>3028.9</v>
+      </c>
+      <c r="J37" s="15">
+        <v>2985.7</v>
+      </c>
+      <c r="K37" s="15">
+        <v>2941.2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="15">
+        <v>1058.0999999999999</v>
+      </c>
+      <c r="G38" s="15">
+        <v>1048.9000000000001</v>
+      </c>
+      <c r="H38" s="15">
+        <v>1060.5999999999999</v>
+      </c>
+      <c r="I38" s="15">
+        <v>1032.5</v>
+      </c>
+      <c r="J38" s="15">
+        <v>995.6</v>
+      </c>
+      <c r="K38" s="15">
+        <v>1013.2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" s="15">
+        <f>+SUM(F33:F38)</f>
+        <v>8283.2999999999993</v>
+      </c>
+      <c r="G39" s="15">
+        <f>+SUM(G33:G38)</f>
+        <v>8331.1</v>
+      </c>
+      <c r="H39" s="15">
+        <f>+SUM(H33:H38)</f>
+        <v>7885.6999999999989</v>
+      </c>
+      <c r="I39" s="15">
+        <f>+SUM(I33:I38)</f>
+        <v>7714.6</v>
+      </c>
+      <c r="J39" s="15">
+        <f>+SUM(J33:J38)</f>
+        <v>7917.1</v>
+      </c>
+      <c r="K39" s="15">
+        <f>+SUM(K33:K38)</f>
+        <v>7867.9</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" s="15">
+        <v>171.8</v>
+      </c>
+      <c r="G41" s="15">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="H41" s="15">
+        <v>193.1</v>
+      </c>
+      <c r="I41" s="15">
+        <v>205.5</v>
+      </c>
+      <c r="J41" s="15">
+        <v>236</v>
+      </c>
+      <c r="K41" s="15">
+        <v>209.3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" s="15">
+        <v>780.5</v>
+      </c>
+      <c r="G42" s="15">
+        <v>788.5</v>
+      </c>
+      <c r="H42" s="15">
+        <v>757.2</v>
+      </c>
+      <c r="I42" s="15">
+        <v>861.2</v>
+      </c>
+      <c r="J42" s="15">
+        <v>928.1</v>
+      </c>
+      <c r="K42" s="15">
+        <v>903.5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" s="15">
+        <v>994.3</v>
+      </c>
+      <c r="G43" s="15">
+        <v>994.7</v>
+      </c>
+      <c r="H43" s="15">
+        <v>995.1</v>
+      </c>
+      <c r="I43" s="15">
+        <v>995.4</v>
+      </c>
+      <c r="J43" s="15">
+        <v>995.8</v>
+      </c>
+      <c r="K43" s="15">
+        <v>996.2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F44" s="15">
+        <v>6336.7</v>
+      </c>
+      <c r="G44" s="15">
+        <v>6400.7</v>
+      </c>
+      <c r="H44" s="15">
+        <v>5940.3</v>
+      </c>
+      <c r="I44" s="15">
+        <v>5652.5</v>
+      </c>
+      <c r="J44" s="15">
+        <v>5757.1</v>
+      </c>
+      <c r="K44" s="15">
+        <v>5758.9</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="15">
+        <f>+SUM(F41:F44)</f>
+        <v>8283.2999999999993</v>
+      </c>
+      <c r="G45" s="15">
+        <f>+SUM(G41:G44)</f>
+        <v>8331.1</v>
+      </c>
+      <c r="H45" s="15">
+        <f>+SUM(H41:H44)</f>
+        <v>7885.7000000000007</v>
+      </c>
+      <c r="I45" s="15">
+        <f>+SUM(I41:I44)</f>
+        <v>7714.6</v>
+      </c>
+      <c r="J45" s="15">
+        <f>+SUM(J41:J44)</f>
+        <v>7917</v>
+      </c>
+      <c r="K45" s="15">
+        <f>+SUM(K41:K44)</f>
+        <v>7867.9</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F47" s="15">
+        <f>(F34/SUM(C6:F6)*365)</f>
+        <v>44.449976065102916</v>
+      </c>
+      <c r="G47" s="15">
+        <f>(G34/SUM(D6:G6)*365)</f>
+        <v>46.922126081582199</v>
+      </c>
+      <c r="H47" s="20">
+        <v>35.9</v>
+      </c>
+      <c r="I47" s="15">
+        <f>(I34/SUM(F6:I6)*365)</f>
+        <v>36.047810155295757</v>
+      </c>
+      <c r="J47" s="15">
+        <f>(J34/SUM(G6:J6)*365)</f>
+        <v>53.416158946879065</v>
+      </c>
+      <c r="K47" s="15">
+        <f>(K34/SUM(H6:K6)*365)</f>
+        <v>35.871527949084808</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48" s="21">
+        <f>(F35/SUM(C7:F7)) * 365</f>
+        <v>116.57659124206414</v>
+      </c>
+      <c r="G48" s="21">
+        <f>(G35/SUM(D7:G7)) * 365</f>
+        <v>106.90715392021436</v>
+      </c>
+      <c r="H48" s="22">
+        <v>117.4</v>
+      </c>
+      <c r="I48" s="21">
+        <f>(I35/SUM(F7:I7)) * 365</f>
+        <v>109.85451989435121</v>
+      </c>
+      <c r="J48" s="21">
+        <f>(J35/SUM(G7:J7)) * 365</f>
+        <v>114.54819527611443</v>
+      </c>
+      <c r="K48" s="21">
+        <f>(K35/SUM(H7:K7)) * 365</f>
+        <v>117.38916359369763</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F49" s="15">
+        <f>+(F41/SUM(C7:F7)) * 365</f>
+        <v>25.519697216343808</v>
+      </c>
+      <c r="G49" s="15">
+        <f>+(G41/SUM(D7:G7)) * 365</f>
+        <v>22.490686089832142</v>
+      </c>
+      <c r="H49" s="20">
+        <v>32</v>
+      </c>
+      <c r="I49" s="15">
+        <f>+(I41/SUM(F7:I7)) * 365</f>
+        <v>31.953437846127635</v>
+      </c>
+      <c r="J49" s="15">
+        <f>+(J41/SUM(G7:J7)) * 365</f>
+        <v>35.820026613439786</v>
+      </c>
+      <c r="K49" s="15">
+        <f>+(K41/SUM(H7:K7)) * 365</f>
+        <v>32.012445524639631</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" s="15">
+        <f>+F47+F48-F49</f>
+        <v>135.50687009082324</v>
+      </c>
+      <c r="G50" s="15">
+        <f>+G47+G48-G49</f>
+        <v>131.33859391196441</v>
+      </c>
+      <c r="H50" s="20">
+        <v>121.2</v>
+      </c>
+      <c r="I50" s="15">
+        <f>+I47+I48-I49</f>
+        <v>113.94889220351934</v>
+      </c>
+      <c r="J50" s="15">
+        <f>+J47+J48-J49</f>
+        <v>132.14432760955373</v>
+      </c>
+      <c r="K50" s="15">
+        <f>+K47+K48-K49</f>
+        <v>121.24824601814281</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="15">
+        <v>774.9</v>
+      </c>
+      <c r="D58" s="15">
+        <v>300.2</v>
+      </c>
+      <c r="E58" s="15">
+        <v>273.5</v>
+      </c>
+      <c r="F58" s="15">
+        <v>476</v>
+      </c>
+      <c r="G58" s="15">
+        <v>377.2</v>
+      </c>
+      <c r="H58" s="15">
+        <v>409.5</v>
+      </c>
+      <c r="I58" s="15">
+        <v>314.10000000000002</v>
+      </c>
+      <c r="J58" s="15">
+        <v>200</v>
+      </c>
+      <c r="K58" s="15">
+        <v>395.5</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B59" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59" s="15">
+        <v>-22.2</v>
+      </c>
+      <c r="D59" s="15">
+        <v>-27.6</v>
+      </c>
+      <c r="E59" s="15">
+        <v>-24.4</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-82.8</v>
+      </c>
+      <c r="G59" s="15">
+        <v>-39</v>
+      </c>
+      <c r="H59" s="15">
+        <v>-38.5</v>
+      </c>
+      <c r="I59" s="15">
+        <v>-61.4</v>
+      </c>
+      <c r="J59" s="15">
+        <v>-56</v>
+      </c>
+      <c r="K59" s="15">
+        <v>-56.5</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B60" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="15">
+        <f t="shared" ref="C60:J60" si="38">+C58+C59</f>
+        <v>752.69999999999993</v>
+      </c>
+      <c r="D60" s="15">
+        <f t="shared" si="38"/>
+        <v>272.59999999999997</v>
+      </c>
+      <c r="E60" s="15">
+        <f t="shared" si="38"/>
+        <v>249.1</v>
+      </c>
+      <c r="F60" s="15">
+        <f t="shared" si="38"/>
+        <v>393.2</v>
+      </c>
+      <c r="G60" s="15">
+        <f t="shared" si="38"/>
+        <v>338.2</v>
+      </c>
+      <c r="H60" s="15">
+        <f t="shared" si="38"/>
+        <v>371</v>
+      </c>
+      <c r="I60" s="15">
+        <f t="shared" si="38"/>
+        <v>252.70000000000002</v>
+      </c>
+      <c r="J60" s="15">
+        <f t="shared" si="38"/>
+        <v>144</v>
+      </c>
+      <c r="K60" s="15">
+        <f>+K58+K59</f>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="15">
+        <f>+C16</f>
+        <v>247.70000000000002</v>
+      </c>
+      <c r="D61" s="15">
+        <f t="shared" ref="D61:K61" si="39">+D16</f>
+        <v>183.49999999999997</v>
+      </c>
+      <c r="E61" s="15">
+        <f t="shared" si="39"/>
+        <v>122.70000000000005</v>
+      </c>
+      <c r="F61" s="15">
+        <f t="shared" si="39"/>
+        <v>193.00000000000011</v>
+      </c>
+      <c r="G61" s="15">
+        <f t="shared" si="39"/>
+        <v>163.79999999999995</v>
+      </c>
+      <c r="H61" s="15">
+        <f t="shared" si="39"/>
+        <v>88.500000000000028</v>
+      </c>
+      <c r="I61" s="15">
+        <f t="shared" si="39"/>
+        <v>106.70000000000002</v>
+      </c>
+      <c r="J61" s="15">
+        <f t="shared" si="39"/>
+        <v>143.20000000000002</v>
+      </c>
+      <c r="K61" s="15">
+        <f t="shared" si="39"/>
+        <v>90.80000000000004</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B64" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F64" s="15">
+        <f t="shared" ref="F64:J64" si="40">+SUM(C60:F60)</f>
+        <v>1667.6</v>
+      </c>
+      <c r="G64" s="15">
+        <f t="shared" si="40"/>
+        <v>1253.0999999999999</v>
+      </c>
+      <c r="H64" s="15">
+        <f t="shared" si="40"/>
+        <v>1351.5</v>
+      </c>
+      <c r="I64" s="15">
+        <f t="shared" si="40"/>
+        <v>1355.1000000000001</v>
+      </c>
+      <c r="J64" s="15">
+        <f t="shared" si="40"/>
+        <v>1105.9000000000001</v>
+      </c>
+      <c r="K64" s="15">
+        <f>+SUM(H60:K60)</f>
+        <v>1106.7</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B65" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F65" s="15">
+        <f t="shared" ref="F65:J65" si="41">+SUM(C61:F61)</f>
+        <v>746.9000000000002</v>
+      </c>
+      <c r="G65" s="15">
+        <f t="shared" si="41"/>
+        <v>663.00000000000011</v>
+      </c>
+      <c r="H65" s="15">
+        <f t="shared" si="41"/>
+        <v>568.00000000000011</v>
+      </c>
+      <c r="I65" s="15">
+        <f t="shared" si="41"/>
+        <v>552.00000000000011</v>
+      </c>
+      <c r="J65" s="15">
+        <f t="shared" si="41"/>
+        <v>502.20000000000005</v>
+      </c>
+      <c r="K65" s="15">
+        <f>+SUM(H61:K61)</f>
+        <v>429.20000000000016</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="F17:W23 AA22:AO22 AL8:AO20 F8:K8 O8:W8 F9:K9 O9:W9 F10:K10 O10:W10 F11:K11 O11:W11 F12:K12 O12:W12 F13:K13 O13:W13 F14:K14 O14:W14 F15:K15 O15:W15 F16:K16 O16:W16 F25:W27 F24:K24 M24:W24 AL21 AN21:AO21" formula="1"/>
+    <ignoredError sqref="AA7:AK7 AK6 H47:K49 AA6" formulaRange="1"/>
+    <ignoredError sqref="AA8:AK20 AK21" formula="1" formulaRange="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Semiconductor/SWKS.xlsx
+++ b/Semiconductor/SWKS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48666112-59E4-CB49-89D8-D2D299A4E94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F87935D-E2C8-DC42-8D95-919C52741A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20820" yWindow="3540" windowWidth="30380" windowHeight="18980" activeTab="1" xr2:uid="{872DC379-8029-6E4A-AB13-AE0B132249A5}"/>
+    <workbookView xWindow="20820" yWindow="3540" windowWidth="30380" windowHeight="18980" xr2:uid="{872DC379-8029-6E4A-AB13-AE0B132249A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="74">
   <si>
     <t>P</t>
   </si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>ROIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contains </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merger </t>
   </si>
 </sst>
 </file>
@@ -263,7 +269,7 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="m/d;@"/>
+    <numFmt numFmtId="166" formatCode="m/d;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -334,7 +340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -345,8 +351,8 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -378,6 +384,7 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -818,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2208B4-D5F3-2D42-AF5A-21BE16CD29C2}">
-  <dimension ref="B2:G16"/>
+  <dimension ref="B2:G17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="30.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.83203125" style="3" customWidth="1"/>
@@ -916,10 +923,21 @@
       <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="C15" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="6" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="23">
+        <v>45958</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2161,27 +2179,27 @@
         <v>429.80000000000018</v>
       </c>
       <c r="G8" s="15">
-        <f>+G6-G7</f>
+        <f t="shared" ref="G8:L8" si="11">+G6-G7</f>
         <v>441.9</v>
       </c>
       <c r="H8" s="15">
-        <f>+H6-H7</f>
+        <f t="shared" si="11"/>
         <v>391.6</v>
       </c>
       <c r="I8" s="15">
-        <f>+I6-I7</f>
+        <f t="shared" si="11"/>
         <v>401</v>
       </c>
       <c r="J8" s="15">
-        <f>+J6-J7</f>
+        <f t="shared" si="11"/>
         <v>447.6</v>
       </c>
       <c r="K8" s="15">
-        <f>+K6-K7</f>
+        <f t="shared" si="11"/>
         <v>427.20000000000005</v>
       </c>
       <c r="L8" s="15">
-        <f>+L6-L7</f>
+        <f t="shared" si="11"/>
         <v>372.21338324754333</v>
       </c>
       <c r="X8" s="2">
@@ -2205,35 +2223,35 @@
         <v>1648.4579999999996</v>
       </c>
       <c r="AC8" s="2">
-        <f t="shared" ref="AC8:AJ8" si="11">+AC6-AC7</f>
+        <f t="shared" ref="AC8:AJ8" si="12">+AC6-AC7</f>
         <v>1615.4888399999995</v>
       </c>
       <c r="AD8" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1583.1790631999993</v>
       </c>
       <c r="AE8" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1551.5154819359996</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1520.4851722972794</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1490.0754688513339</v>
       </c>
       <c r="AH8" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1460.273959474307</v>
       </c>
       <c r="AI8" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1431.0684802848209</v>
       </c>
       <c r="AJ8" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1402.4471106791245</v>
       </c>
     </row>
@@ -2430,27 +2448,27 @@
         <v>192.30000000000018</v>
       </c>
       <c r="G11" s="15">
-        <f>+G8-SUM(G9:G10)</f>
+        <f t="shared" ref="G11:L11" si="13">+G8-SUM(G9:G10)</f>
         <v>182.89999999999998</v>
       </c>
       <c r="H11" s="15">
-        <f>+H8-SUM(H9:H10)</f>
+        <f t="shared" si="13"/>
         <v>117.10000000000002</v>
       </c>
       <c r="I11" s="15">
-        <f>+I8-SUM(I9:I10)</f>
+        <f t="shared" si="13"/>
         <v>112.30000000000001</v>
       </c>
       <c r="J11" s="15">
-        <f>+J8-SUM(J9:J10)</f>
+        <f t="shared" si="13"/>
         <v>112.80000000000001</v>
       </c>
       <c r="K11" s="15">
-        <f>+K8-SUM(K9:K10)</f>
+        <f t="shared" si="13"/>
         <v>115.40000000000003</v>
       </c>
       <c r="L11" s="15">
-        <f>+L8-SUM(L9:L10)</f>
+        <f t="shared" si="13"/>
         <v>154.05708937763225</v>
       </c>
       <c r="X11" s="2">
@@ -2474,35 +2492,35 @@
         <v>514.59799999999973</v>
       </c>
       <c r="AC11" s="2">
-        <f t="shared" ref="AC11:AJ11" si="12">+AC8-SUM(AC9:AC10)</f>
+        <f t="shared" ref="AC11:AJ11" si="14">+AC8-SUM(AC9:AC10)</f>
         <v>504.30603999999971</v>
       </c>
       <c r="AD11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>494.21991919999937</v>
       </c>
       <c r="AE11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>484.33552081599964</v>
       </c>
       <c r="AF11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>474.64881039967963</v>
       </c>
       <c r="AG11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>465.15583419168615</v>
       </c>
       <c r="AH11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>455.85271750785228</v>
       </c>
       <c r="AI11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>446.73566315769517</v>
       </c>
       <c r="AJ11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>437.80094989454142</v>
       </c>
     </row>
@@ -2699,27 +2717,27 @@
         <v>191.20000000000016</v>
       </c>
       <c r="G14" s="15">
-        <f>+SUM(G11:G13)</f>
+        <f t="shared" ref="G14:L14" si="15">+SUM(G11:G13)</f>
         <v>192.19999999999996</v>
       </c>
       <c r="H14" s="15">
-        <f>+SUM(H11:H13)</f>
+        <f t="shared" si="15"/>
         <v>122.20000000000003</v>
       </c>
       <c r="I14" s="15">
-        <f>+SUM(I11:I13)</f>
+        <f t="shared" si="15"/>
         <v>113.70000000000002</v>
       </c>
       <c r="J14" s="15">
-        <f>+SUM(J11:J13)</f>
+        <f t="shared" si="15"/>
         <v>123.80000000000001</v>
       </c>
       <c r="K14" s="15">
-        <f>+SUM(K11:K13)</f>
+        <f t="shared" si="15"/>
         <v>121.30000000000004</v>
       </c>
       <c r="L14" s="15">
-        <f>+SUM(L11:L13)</f>
+        <f t="shared" si="15"/>
         <v>161.89050070191865</v>
       </c>
       <c r="X14" s="2">
@@ -2743,35 +2761,35 @@
         <v>540.86199999999974</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" ref="AC14:AJ14" si="13">+SUM(AC11:AC13)</f>
+        <f t="shared" ref="AC14:AJ14" si="16">+SUM(AC11:AC13)</f>
         <v>530.04475999999977</v>
       </c>
       <c r="AD14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>519.44386479999935</v>
       </c>
       <c r="AE14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>509.05498750399966</v>
       </c>
       <c r="AF14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>498.87388775391963</v>
       </c>
       <c r="AG14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>488.89640999884136</v>
       </c>
       <c r="AH14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>479.11848179886437</v>
       </c>
       <c r="AI14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>469.53611216288704</v>
       </c>
       <c r="AJ14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>460.14538991962945</v>
       </c>
     </row>
@@ -2829,35 +2847,35 @@
         <v>48.705999999999968</v>
       </c>
       <c r="AC15" s="2">
-        <f t="shared" ref="AC15:AJ15" si="14">+AC14*(AB15/AB14)</f>
+        <f t="shared" ref="AC15:AJ15" si="17">+AC14*(AB15/AB14)</f>
         <v>47.731879999999968</v>
       </c>
       <c r="AD15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>46.777242399999935</v>
       </c>
       <c r="AE15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>45.841697551999957</v>
       </c>
       <c r="AF15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>44.924863600959959</v>
       </c>
       <c r="AG15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>44.026366328940767</v>
       </c>
       <c r="AH15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>43.145839002361939</v>
       </c>
       <c r="AI15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>42.282922222314696</v>
       </c>
       <c r="AJ15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>41.437263777868417</v>
       </c>
     </row>
@@ -2882,27 +2900,27 @@
         <v>193.00000000000011</v>
       </c>
       <c r="G16" s="15">
-        <f>+G14-G15</f>
+        <f t="shared" ref="G16:L16" si="18">+G14-G15</f>
         <v>163.79999999999995</v>
       </c>
       <c r="H16" s="15">
-        <f>+H14-H15</f>
+        <f t="shared" si="18"/>
         <v>88.500000000000028</v>
       </c>
       <c r="I16" s="15">
-        <f>+I14-I15</f>
+        <f t="shared" si="18"/>
         <v>106.70000000000002</v>
       </c>
       <c r="J16" s="15">
-        <f>+J14-J15</f>
+        <f t="shared" si="18"/>
         <v>143.20000000000002</v>
       </c>
       <c r="K16" s="15">
-        <f>+K14-K15</f>
+        <f t="shared" si="18"/>
         <v>90.80000000000004</v>
       </c>
       <c r="L16" s="15">
-        <f>+L14-L15</f>
+        <f t="shared" si="18"/>
         <v>121.41787552643899</v>
       </c>
       <c r="X16" s="2">
@@ -2926,35 +2944,35 @@
         <v>492.15599999999978</v>
       </c>
       <c r="AC16" s="2">
-        <f t="shared" ref="AC16:AJ16" si="15">+AC14-AC15</f>
+        <f t="shared" ref="AC16:AJ16" si="19">+AC14-AC15</f>
         <v>482.31287999999978</v>
       </c>
       <c r="AD16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>472.66662239999943</v>
       </c>
       <c r="AE16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>463.21328995199968</v>
       </c>
       <c r="AF16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>453.94902415295968</v>
       </c>
       <c r="AG16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>444.87004366990061</v>
       </c>
       <c r="AH16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>435.97264279650244</v>
       </c>
       <c r="AI16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>427.25318994057233</v>
       </c>
       <c r="AJ16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>418.70812614176106</v>
       </c>
       <c r="AK16" s="2">
@@ -2962,803 +2980,803 @@
         <v>422.89520740317869</v>
       </c>
       <c r="AL16" s="2">
-        <f t="shared" ref="AL16:CW16" si="16">+AK16*(1+$AN$22)</f>
+        <f t="shared" ref="AL16:CW16" si="20">+AK16*(1+$AN$22)</f>
         <v>427.12415947721047</v>
       </c>
       <c r="AM16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>431.39540107198258</v>
       </c>
       <c r="AN16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>435.70935508270242</v>
       </c>
       <c r="AO16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>440.06644863352943</v>
       </c>
       <c r="AP16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>444.46711311986473</v>
       </c>
       <c r="AQ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>448.91178425106341</v>
       </c>
       <c r="AR16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>453.40090209357408</v>
       </c>
       <c r="AS16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>457.93491111450982</v>
       </c>
       <c r="AT16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>462.51426022565494</v>
       </c>
       <c r="AU16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>467.13940282791151</v>
       </c>
       <c r="AV16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>471.81079685619062</v>
       </c>
       <c r="AW16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>476.52890482475254</v>
       </c>
       <c r="AX16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>481.2941938730001</v>
       </c>
       <c r="AY16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>486.10713581173007</v>
       </c>
       <c r="AZ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>490.9682071698474</v>
       </c>
       <c r="BA16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>495.87788924154586</v>
       </c>
       <c r="BB16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>500.83666813396133</v>
       </c>
       <c r="BC16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>505.84503481530095</v>
       </c>
       <c r="BD16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>510.90348516345398</v>
       </c>
       <c r="BE16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>516.01252001508851</v>
       </c>
       <c r="BF16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>521.17264521523941</v>
       </c>
       <c r="BG16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>526.38437166739186</v>
       </c>
       <c r="BH16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>531.64821538406579</v>
       </c>
       <c r="BI16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>536.96469753790643</v>
       </c>
       <c r="BJ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>542.33434451328549</v>
       </c>
       <c r="BK16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>547.75768795841839</v>
       </c>
       <c r="BL16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>553.23526483800254</v>
       </c>
       <c r="BM16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>558.76761748638262</v>
       </c>
       <c r="BN16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>564.35529366124649</v>
       </c>
       <c r="BO16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>569.99884659785891</v>
       </c>
       <c r="BP16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>575.69883506383746</v>
       </c>
       <c r="BQ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>581.45582341447584</v>
       </c>
       <c r="BR16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>587.27038164862063</v>
       </c>
       <c r="BS16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>593.14308546510688</v>
       </c>
       <c r="BT16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>599.074516319758</v>
       </c>
       <c r="BU16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>605.06526148295563</v>
       </c>
       <c r="BV16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>611.11591409778521</v>
       </c>
       <c r="BW16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>617.22707323876307</v>
       </c>
       <c r="BX16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>623.39934397115076</v>
       </c>
       <c r="BY16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>629.63333741086228</v>
       </c>
       <c r="BZ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>635.92967078497088</v>
       </c>
       <c r="CA16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>642.28896749282057</v>
       </c>
       <c r="CB16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>648.7118571677488</v>
       </c>
       <c r="CC16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>655.19897573942626</v>
       </c>
       <c r="CD16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>661.75096549682053</v>
       </c>
       <c r="CE16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>668.36847515178874</v>
       </c>
       <c r="CF16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>675.05215990330669</v>
       </c>
       <c r="CG16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>681.80268150233974</v>
       </c>
       <c r="CH16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>688.6207083173631</v>
       </c>
       <c r="CI16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>695.50691540053674</v>
       </c>
       <c r="CJ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>702.46198455454214</v>
       </c>
       <c r="CK16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>709.48660440008757</v>
       </c>
       <c r="CL16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>716.5814704440885</v>
       </c>
       <c r="CM16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>723.74728514852939</v>
       </c>
       <c r="CN16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>730.98475800001472</v>
       </c>
       <c r="CO16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>738.29460558001483</v>
       </c>
       <c r="CP16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>745.67755163581501</v>
       </c>
       <c r="CQ16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>753.13432715217311</v>
       </c>
       <c r="CR16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>760.66567042369491</v>
       </c>
       <c r="CS16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>768.27232712793182</v>
       </c>
       <c r="CT16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>775.95505039921113</v>
       </c>
       <c r="CU16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>783.71460090320329</v>
       </c>
       <c r="CV16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>791.55174691223533</v>
       </c>
       <c r="CW16" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>799.46726438135772</v>
       </c>
       <c r="CX16" s="2">
-        <f t="shared" ref="CX16:FC16" si="17">+CW16*(1+$AN$22)</f>
+        <f t="shared" ref="CX16:FC16" si="21">+CW16*(1+$AN$22)</f>
         <v>807.46193702517132</v>
       </c>
       <c r="CY16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>815.53655639542308</v>
       </c>
       <c r="CZ16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>823.69192195937728</v>
       </c>
       <c r="DA16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>831.92884117897108</v>
       </c>
       <c r="DB16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>840.24812959076075</v>
       </c>
       <c r="DC16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>848.65061088666835</v>
       </c>
       <c r="DD16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>857.13711699553505</v>
       </c>
       <c r="DE16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>865.70848816549039</v>
       </c>
       <c r="DF16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>874.36557304714529</v>
       </c>
       <c r="DG16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>883.10922877761675</v>
       </c>
       <c r="DH16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>891.94032106539294</v>
       </c>
       <c r="DI16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>900.8597242760469</v>
       </c>
       <c r="DJ16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>909.86832151880742</v>
       </c>
       <c r="DK16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>918.96700473399551</v>
       </c>
       <c r="DL16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>928.15667478133548</v>
       </c>
       <c r="DM16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>937.43824152914885</v>
       </c>
       <c r="DN16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>946.81262394444036</v>
       </c>
       <c r="DO16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>956.28075018388472</v>
       </c>
       <c r="DP16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>965.84355768572357</v>
       </c>
       <c r="DQ16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>975.50199326258087</v>
       </c>
       <c r="DR16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>985.2570131952067</v>
       </c>
       <c r="DS16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>995.10958332715882</v>
       </c>
       <c r="DT16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1005.0606791604304</v>
       </c>
       <c r="DU16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1015.1112859520347</v>
       </c>
       <c r="DV16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1025.2623988115549</v>
       </c>
       <c r="DW16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1035.5150227996705</v>
       </c>
       <c r="DX16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1045.8701730276673</v>
       </c>
       <c r="DY16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1056.328874757944</v>
       </c>
       <c r="DZ16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1066.8921635055235</v>
       </c>
       <c r="EA16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1077.5610851405788</v>
       </c>
       <c r="EB16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1088.3366959919847</v>
       </c>
       <c r="EC16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1099.2200629519045</v>
       </c>
       <c r="ED16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1110.2122635814235</v>
       </c>
       <c r="EE16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1121.3143862172378</v>
       </c>
       <c r="EF16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1132.5275300794103</v>
       </c>
       <c r="EG16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1143.8528053802045</v>
       </c>
       <c r="EH16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1155.2913334340064</v>
       </c>
       <c r="EI16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1166.8442467683465</v>
       </c>
       <c r="EJ16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1178.5126892360299</v>
       </c>
       <c r="EK16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1190.2978161283902</v>
       </c>
       <c r="EL16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1202.2007942896741</v>
       </c>
       <c r="EM16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1214.222802232571</v>
       </c>
       <c r="EN16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1226.3650302548967</v>
       </c>
       <c r="EO16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1238.6286805574457</v>
       </c>
       <c r="EP16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1251.0149673630201</v>
       </c>
       <c r="EQ16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1263.5251170366503</v>
       </c>
       <c r="ER16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1276.1603682070167</v>
       </c>
       <c r="ES16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1288.921971889087</v>
       </c>
       <c r="ET16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1301.8111916079779</v>
       </c>
       <c r="EU16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1314.8293035240577</v>
       </c>
       <c r="EV16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1327.9775965592983</v>
       </c>
       <c r="EW16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1341.2573725248913</v>
       </c>
       <c r="EX16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1354.6699462501401</v>
       </c>
       <c r="EY16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1368.2166457126416</v>
       </c>
       <c r="EZ16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1381.898812169768</v>
       </c>
       <c r="FA16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1395.7178002914657</v>
       </c>
       <c r="FB16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1409.6749782943803</v>
       </c>
       <c r="FC16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1423.771728077324</v>
       </c>
       <c r="FD16" s="2">
-        <f t="shared" ref="FD16:GP16" si="18">+FC16*(1+$AN$22)</f>
+        <f t="shared" ref="FD16:GP16" si="22">+FC16*(1+$AN$22)</f>
         <v>1438.0094453580973</v>
       </c>
       <c r="FE16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1452.3895398116783</v>
       </c>
       <c r="FF16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1466.9134352097951</v>
       </c>
       <c r="FG16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1481.582569561893</v>
       </c>
       <c r="FH16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1496.398395257512</v>
       </c>
       <c r="FI16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1511.3623792100871</v>
       </c>
       <c r="FJ16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1526.476003002188</v>
       </c>
       <c r="FK16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1541.74076303221</v>
       </c>
       <c r="FL16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1557.158170662532</v>
       </c>
       <c r="FM16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1572.7297523691573</v>
       </c>
       <c r="FN16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1588.4570498928488</v>
       </c>
       <c r="FO16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1604.3416203917773</v>
       </c>
       <c r="FP16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1620.3850365956951</v>
       </c>
       <c r="FQ16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1636.588886961652</v>
       </c>
       <c r="FR16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1652.9547758312685</v>
       </c>
       <c r="FS16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1669.4843235895812</v>
       </c>
       <c r="FT16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1686.1791668254771</v>
       </c>
       <c r="FU16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1703.0409584937318</v>
       </c>
       <c r="FV16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1720.0713680786691</v>
       </c>
       <c r="FW16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1737.2720817594559</v>
       </c>
       <c r="FX16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1754.6448025770505</v>
       </c>
       <c r="FY16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1772.1912506028211</v>
       </c>
       <c r="FZ16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1789.9131631088494</v>
       </c>
       <c r="GA16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1807.8122947399379</v>
       </c>
       <c r="GB16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1825.8904176873373</v>
       </c>
       <c r="GC16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1844.1493218642106</v>
       </c>
       <c r="GD16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1862.5908150828527</v>
       </c>
       <c r="GE16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1881.2167232336813</v>
       </c>
       <c r="GF16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1900.0288904660181</v>
       </c>
       <c r="GG16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1919.0291793706783</v>
       </c>
       <c r="GH16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1938.2194711643851</v>
       </c>
       <c r="GI16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1957.6016658760291</v>
       </c>
       <c r="GJ16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1977.1776825347895</v>
       </c>
       <c r="GK16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1996.9494593601373</v>
       </c>
       <c r="GL16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2016.9189539537388</v>
       </c>
       <c r="GM16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2037.0881434932762</v>
       </c>
       <c r="GN16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2057.4590249282091</v>
       </c>
       <c r="GO16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2078.0336151774914</v>
       </c>
       <c r="GP16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>2098.8139513292663</v>
       </c>
       <c r="GQ16" s="2">
-        <f t="shared" ref="GQ16:HX16" si="19">+GP16*(1+$AN$22)</f>
+        <f t="shared" ref="GQ16:HX16" si="23">+GP16*(1+$AN$22)</f>
         <v>2119.8020908425588</v>
       </c>
       <c r="GR16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2141.0001117509842</v>
       </c>
       <c r="GS16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2162.4101128684938</v>
       </c>
       <c r="GT16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2184.0342139971785</v>
       </c>
       <c r="GU16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2205.8745561371502</v>
       </c>
       <c r="GV16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2227.9333016985215</v>
       </c>
       <c r="GW16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2250.2126347155067</v>
       </c>
       <c r="GX16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2272.7147610626616</v>
       </c>
       <c r="GY16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2295.4419086732883</v>
       </c>
       <c r="GZ16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2318.396327760021</v>
       </c>
       <c r="HA16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2341.580291037621</v>
       </c>
       <c r="HB16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2364.9960939479975</v>
       </c>
       <c r="HC16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2388.6460548874775</v>
       </c>
       <c r="HD16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2412.5325154363522</v>
       </c>
       <c r="HE16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2436.6578405907158</v>
       </c>
       <c r="HF16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2461.0244189966229</v>
       </c>
       <c r="HG16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2485.634663186589</v>
       </c>
       <c r="HH16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2510.491009818455</v>
       </c>
       <c r="HI16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2535.5959199166396</v>
       </c>
       <c r="HJ16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2560.9518791158062</v>
       </c>
       <c r="HK16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2586.5613979069644</v>
       </c>
       <c r="HL16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2612.4270118860341</v>
       </c>
       <c r="HM16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2638.5512820048943</v>
       </c>
       <c r="HN16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2664.9367948249433</v>
       </c>
       <c r="HO16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2691.5861627731929</v>
       </c>
       <c r="HP16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2718.5020244009247</v>
       </c>
       <c r="HQ16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2745.6870446449338</v>
       </c>
       <c r="HR16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2773.1439150913834</v>
       </c>
       <c r="HS16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2800.8753542422974</v>
       </c>
       <c r="HT16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2828.8841077847205</v>
       </c>
       <c r="HU16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2857.1729488625679</v>
       </c>
       <c r="HV16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2885.7446783511937</v>
       </c>
       <c r="HW16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2914.6021251347056</v>
       </c>
       <c r="HX16" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>2943.7481463860527</v>
       </c>
       <c r="HY16" s="2">
-        <f t="shared" ref="HY16:IB16" si="20">+HX16*(1+$AN$22)</f>
+        <f t="shared" ref="HY16:IB16" si="24">+HX16*(1+$AN$22)</f>
         <v>2973.1856278499131</v>
       </c>
       <c r="HZ16" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>3002.9174841284121</v>
       </c>
       <c r="IA16" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>3032.9466589696963</v>
       </c>
       <c r="IB16" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>3063.2761255593932</v>
       </c>
       <c r="XFD16" s="2">
-        <f t="shared" ref="XFD16" si="21">+XFC16*(1+$AN$22)</f>
+        <f t="shared" ref="XFD16" si="25">+XFC16*(1+$AN$22)</f>
         <v>0</v>
       </c>
     </row>
@@ -3777,39 +3795,39 @@
         <v>34</v>
       </c>
       <c r="C20" s="16">
-        <f t="shared" ref="C20:J20" si="22">+C8/C6</f>
+        <f t="shared" ref="C20:J20" si="26">+C8/C6</f>
         <v>0.42163961714523512</v>
       </c>
       <c r="D20" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.40181644359464624</v>
       </c>
       <c r="E20" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.40209828823854227</v>
       </c>
       <c r="F20" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.41931707317073186</v>
       </c>
       <c r="G20" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.41357042583060361</v>
       </c>
       <c r="H20" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.4108266890474192</v>
       </c>
       <c r="I20" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.41554404145077722</v>
       </c>
       <c r="J20" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.40683512088711143</v>
       </c>
       <c r="K20" s="16">
-        <f t="shared" ref="K20" si="23">+K8/K6</f>
+        <f t="shared" ref="K20" si="27">+K8/K6</f>
         <v>0.4125941665056983</v>
       </c>
       <c r="L20" s="16"/>
@@ -3820,51 +3838,51 @@
         <v>0.47476073284112663</v>
       </c>
       <c r="Y20" s="5">
-        <f t="shared" ref="Y20:AJ20" si="24">+Y8/Y6</f>
+        <f t="shared" ref="Y20:AJ20" si="28">+Y8/Y6</f>
         <v>0.44155980219596008</v>
       </c>
       <c r="Z20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41187170895165154</v>
       </c>
       <c r="AA20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465099</v>
       </c>
       <c r="AB20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465093</v>
       </c>
       <c r="AC20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465088</v>
       </c>
       <c r="AD20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465082</v>
       </c>
       <c r="AE20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465093</v>
       </c>
       <c r="AF20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465088</v>
       </c>
       <c r="AG20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465093</v>
       </c>
       <c r="AH20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465088</v>
       </c>
       <c r="AI20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465082</v>
       </c>
       <c r="AJ20" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.41158335168465088</v>
       </c>
     </row>
@@ -3877,90 +3895,90 @@
         <v>7.6091010816859372E-2</v>
       </c>
       <c r="D21" s="16">
-        <f t="shared" ref="D21:J21" si="25">+D15/D14</f>
+        <f t="shared" ref="D21:J21" si="29">+D15/D14</f>
         <v>4.8236514522821586E-2</v>
       </c>
       <c r="E21" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>9.2455621301775121E-2</v>
       </c>
       <c r="F21" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>-9.4142259414226083E-3</v>
       </c>
       <c r="G21" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0.14776274713839752</v>
       </c>
       <c r="H21" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0.27577741407528639</v>
       </c>
       <c r="I21" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>6.1565523306948103E-2</v>
       </c>
       <c r="J21" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>-0.15670436187399028</v>
       </c>
       <c r="K21" s="16">
-        <f t="shared" ref="K21" si="26">+K15/K14</f>
+        <f t="shared" ref="K21" si="30">+K15/K14</f>
         <v>0.25144270403957125</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
       <c r="X21" s="16">
-        <f t="shared" ref="X21:AJ21" si="27">+X15/X14</f>
+        <f t="shared" ref="X21:AJ21" si="31">+X15/X14</f>
         <v>0.12538911717096252</v>
       </c>
       <c r="Y21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8.4188371481189184E-2</v>
       </c>
       <c r="Z21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5.131461958592657E-2</v>
       </c>
       <c r="AA21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AB21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AC21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AD21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AE21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AF21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AG21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AH21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AI21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AJ21" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9.0052545751041838E-2</v>
       </c>
       <c r="AM21" s="5" t="s">
@@ -3976,87 +3994,87 @@
         <v>0.22863087806908036</v>
       </c>
       <c r="D22" s="13">
-        <f t="shared" ref="D22:J22" si="28">+D11/D6</f>
+        <f t="shared" ref="D22:J22" si="32">+D11/D6</f>
         <v>0.1807839388145315</v>
       </c>
       <c r="E22" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0.14599668691330761</v>
       </c>
       <c r="F22" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0.18760975609756114</v>
       </c>
       <c r="G22" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0.17117454375292465</v>
       </c>
       <c r="H22" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0.12284934955937896</v>
       </c>
       <c r="I22" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0.11637305699481866</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0.10252681330667152</v>
       </c>
       <c r="K22" s="13">
-        <f t="shared" ref="K22" si="29">+K11/K6</f>
+        <f t="shared" ref="K22" si="33">+K11/K6</f>
         <v>0.11145451033417039</v>
       </c>
       <c r="X22" s="4">
-        <f t="shared" ref="X22:AJ22" si="30">+X11/X6</f>
+        <f t="shared" ref="X22:AJ22" si="34">+X11/X6</f>
         <v>0.30199617172545806</v>
       </c>
       <c r="Y22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.24861704802615034</v>
       </c>
       <c r="Z22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.1886787936811872</v>
       </c>
       <c r="AA22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573763</v>
       </c>
       <c r="AB22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573754</v>
       </c>
       <c r="AC22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573754</v>
       </c>
       <c r="AD22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573746</v>
       </c>
       <c r="AE22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573754</v>
       </c>
       <c r="AF22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573754</v>
       </c>
       <c r="AG22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573757</v>
       </c>
       <c r="AH22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573751</v>
       </c>
       <c r="AI22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573749</v>
       </c>
       <c r="AJ22" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.12848369179573754</v>
       </c>
       <c r="AM22" s="2" t="s">
@@ -4086,77 +4104,77 @@
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
       <c r="G24" s="16">
-        <f t="shared" ref="G24:L26" si="31">+G6/C6-1</f>
+        <f t="shared" ref="G24:L26" si="35">+G6/C6-1</f>
         <v>-0.11069496462754891</v>
       </c>
       <c r="H24" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-8.8718929254302026E-2</v>
       </c>
       <c r="I24" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>6.5709552733296483E-2</v>
       </c>
       <c r="J24" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>7.3365853658536651E-2</v>
       </c>
       <c r="K24" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-3.0978006551239945E-2</v>
       </c>
       <c r="L24" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-5.5812001678556489E-2</v>
       </c>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
       <c r="Y24" s="4">
-        <f>+Y6/X6-1</f>
+        <f t="shared" ref="Y24:AH24" si="36">+Y6/X6-1</f>
         <v>-0.12999726551818436</v>
       </c>
       <c r="Z24" s="4">
-        <f>+Z6/Y6-1</f>
+        <f t="shared" si="36"/>
         <v>-0.12454949291760953</v>
       </c>
       <c r="AA24" s="4">
-        <f>+AA6/Z6-1</f>
+        <f t="shared" si="36"/>
         <v>-2.1804691239827756E-2</v>
       </c>
       <c r="AB24" s="4">
-        <f>+AB6/AA6-1</f>
+        <f t="shared" si="36"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AC24" s="4">
-        <f>+AC6/AB6-1</f>
+        <f t="shared" si="36"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AD24" s="4">
-        <f>+AD6/AC6-1</f>
+        <f t="shared" si="36"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AE24" s="4">
-        <f>+AE6/AD6-1</f>
+        <f t="shared" si="36"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AF24" s="4">
-        <f>+AF6/AE6-1</f>
+        <f t="shared" si="36"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AG24" s="4">
-        <f>+AG6/AF6-1</f>
+        <f t="shared" si="36"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AH24" s="4">
-        <f>+AH6/AG6-1</f>
+        <f t="shared" si="36"/>
         <v>-1.9999999999999907E-2</v>
       </c>
       <c r="AI24" s="4">
-        <f t="shared" ref="AB24:AJ24" si="32">+AI6/AH6-1</f>
+        <f t="shared" ref="AI24:AJ24" si="37">+AI6/AH6-1</f>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AJ24" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AM24" s="4" t="s">
@@ -4176,66 +4194,66 @@
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-9.8287523384659625E-2</v>
       </c>
       <c r="H25" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-0.10244526130733578</v>
       </c>
       <c r="I25" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>4.1743627632065072E-2</v>
       </c>
       <c r="J25" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>9.6438172043011194E-2</v>
       </c>
       <c r="K25" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-2.9364826045323977E-2</v>
       </c>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
       <c r="Y25" s="4">
-        <f>+Y7/X7-1</f>
+        <f t="shared" ref="Y25:AH25" si="38">+Y7/X7-1</f>
         <v>-7.5003470776065506E-2</v>
       </c>
       <c r="Z25" s="4">
-        <f>+Z7/Y7-1</f>
+        <f t="shared" si="38"/>
         <v>-7.8008329893812678E-2</v>
       </c>
       <c r="AA25" s="4">
-        <f>+AA7/Z7-1</f>
+        <f t="shared" si="38"/>
         <v>-2.1325085463128612E-2</v>
       </c>
       <c r="AB25" s="4">
-        <f>+AB7/AA7-1</f>
+        <f t="shared" si="38"/>
         <v>-2.000000000000024E-2</v>
       </c>
       <c r="AC25" s="4">
-        <f>+AC7/AB7-1</f>
+        <f t="shared" si="38"/>
         <v>-1.9999999999999907E-2</v>
       </c>
       <c r="AD25" s="4">
-        <f>+AD7/AC7-1</f>
+        <f t="shared" si="38"/>
         <v>-1.9999999999999907E-2</v>
       </c>
       <c r="AE25" s="4">
-        <f>+AE7/AD7-1</f>
+        <f t="shared" si="38"/>
         <v>-2.0000000000000129E-2</v>
       </c>
       <c r="AF25" s="4">
-        <f>+AF7/AE7-1</f>
+        <f t="shared" si="38"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AG25" s="4">
-        <f>+AG7/AF7-1</f>
+        <f t="shared" si="38"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AH25" s="4">
-        <f>+AH7/AG7-1</f>
+        <f t="shared" si="38"/>
         <v>-1.9999999999999907E-2</v>
       </c>
       <c r="AM25" s="4" t="s">
@@ -4255,66 +4273,66 @@
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
       <c r="G26" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-0.12771417291748921</v>
       </c>
       <c r="H26" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-6.8284558648584182E-2</v>
       </c>
       <c r="I26" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0.10134578412524031</v>
       </c>
       <c r="J26" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>4.141461144718428E-2</v>
       </c>
       <c r="K26" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-3.3265444670739885E-2</v>
       </c>
       <c r="L26" s="13"/>
       <c r="M26" s="13"/>
       <c r="N26" s="13"/>
       <c r="Y26" s="4">
-        <f>+Y8/X8-1</f>
+        <f t="shared" ref="Y26:AH26" si="39">+Y8/X8-1</f>
         <v>-0.19083822908267112</v>
       </c>
       <c r="Z26" s="4">
-        <f>+Z8/Y8-1</f>
+        <f t="shared" si="39"/>
         <v>-0.18341005077587413</v>
       </c>
       <c r="AA26" s="4">
-        <f>+AA8/Z8-1</f>
+        <f t="shared" si="39"/>
         <v>-2.2489539748954179E-2</v>
       </c>
       <c r="AB26" s="4">
-        <f>+AB8/AA8-1</f>
+        <f t="shared" si="39"/>
         <v>-2.0000000000000129E-2</v>
       </c>
       <c r="AC26" s="4">
-        <f>+AC8/AB8-1</f>
+        <f t="shared" si="39"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AD26" s="4">
-        <f>+AD8/AC8-1</f>
+        <f t="shared" si="39"/>
         <v>-2.0000000000000129E-2</v>
       </c>
       <c r="AE26" s="4">
-        <f>+AE8/AD8-1</f>
+        <f t="shared" si="39"/>
         <v>-1.9999999999999796E-2</v>
       </c>
       <c r="AF26" s="4">
-        <f>+AF8/AE8-1</f>
+        <f t="shared" si="39"/>
         <v>-2.0000000000000129E-2</v>
       </c>
       <c r="AG26" s="4">
-        <f>+AG8/AF8-1</f>
+        <f t="shared" si="39"/>
         <v>-1.9999999999999907E-2</v>
       </c>
       <c r="AH26" s="4">
-        <f>+AH8/AG8-1</f>
+        <f t="shared" si="39"/>
         <v>-2.0000000000000129E-2</v>
       </c>
       <c r="AM26" s="7" t="s">
@@ -4342,187 +4360,187 @@
     </row>
     <row r="29" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C29" s="13">
-        <f t="shared" ref="C29:H29" si="33">+C9/C$6</f>
+        <f t="shared" ref="C29:H29" si="40">+C9/C$6</f>
         <v>0.12742405326674988</v>
       </c>
       <c r="D29" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v>0.14760994263862334</v>
       </c>
       <c r="E29" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v>0.17747101049144118</v>
       </c>
       <c r="F29" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v>0.15951219512195128</v>
       </c>
       <c r="G29" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v>0.16509124941506786</v>
       </c>
       <c r="H29" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v>0.19565673520772134</v>
       </c>
       <c r="I29" s="13">
-        <f>+I9/I$6</f>
+        <f t="shared" ref="I29:K30" si="41">+I9/I$6</f>
         <v>0.20663212435233161</v>
       </c>
       <c r="J29" s="13">
-        <f>+J9/J$6</f>
+        <f t="shared" si="41"/>
         <v>0.20278131248863843</v>
       </c>
       <c r="K29" s="13">
-        <f>+K9/K$6</f>
+        <f t="shared" si="41"/>
         <v>0.19644581804133668</v>
       </c>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
       <c r="N29" s="13"/>
       <c r="X29" s="4">
-        <f t="shared" ref="X29:AB30" si="34">+X9/X$6</f>
+        <f t="shared" ref="X29:AB30" si="42">+X9/X$6</f>
         <v>0.11264242092790082</v>
       </c>
       <c r="Y29" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.12714776632302405</v>
       </c>
       <c r="Z29" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.15119674485399714</v>
       </c>
       <c r="AA29" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.19217499816486824</v>
       </c>
       <c r="AB29" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.19217499816486824</v>
       </c>
       <c r="AC29" s="4">
-        <f t="shared" ref="AC29:AJ29" si="35">+AC9/AC$6</f>
+        <f t="shared" ref="AC29:AJ29" si="43">+AC9/AC$6</f>
         <v>0.19217499816486824</v>
       </c>
       <c r="AD29" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.19217499816486824</v>
       </c>
       <c r="AE29" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.19217499816486824</v>
       </c>
       <c r="AF29" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.19217499816486824</v>
       </c>
       <c r="AG29" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.19217499816486822</v>
       </c>
       <c r="AH29" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.19217499816486822</v>
       </c>
       <c r="AI29" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.19217499816486822</v>
       </c>
       <c r="AJ29" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.19217499816486822</v>
       </c>
     </row>
     <row r="30" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C30" s="13">
-        <f t="shared" ref="C30:H30" si="36">+C10/C$6</f>
+        <f t="shared" ref="C30:H30" si="44">+C10/C$6</f>
         <v>6.5584685809404908E-2</v>
       </c>
       <c r="D30" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>7.3422562141491399E-2</v>
       </c>
       <c r="E30" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>7.8630590833793493E-2</v>
       </c>
       <c r="F30" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>7.2195121951219507E-2</v>
       </c>
       <c r="G30" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>7.7304632662611131E-2</v>
       </c>
       <c r="H30" s="13">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>9.2320604280318921E-2</v>
       </c>
       <c r="I30" s="13">
-        <f>+I10/I$6</f>
+        <f t="shared" si="41"/>
         <v>9.2538860103626941E-2</v>
       </c>
       <c r="J30" s="13">
-        <f>+J10/J$6</f>
+        <f t="shared" si="41"/>
         <v>0.10152699509180149</v>
       </c>
       <c r="K30" s="13">
-        <f>+K10/K$6</f>
+        <f t="shared" si="41"/>
         <v>0.10469383813019123</v>
       </c>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
       <c r="N30" s="13"/>
       <c r="X30" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>6.012214018776775E-2</v>
       </c>
       <c r="Y30" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>6.5794987846785682E-2</v>
       </c>
       <c r="Z30" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>7.1996170416467206E-2</v>
       </c>
       <c r="AA30" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AB30" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AC30" s="4">
-        <f t="shared" ref="AC30:AJ30" si="37">+AC10/AC$6</f>
+        <f t="shared" ref="AC30:AJ30" si="45">+AC10/AC$6</f>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AD30" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AE30" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AF30" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AG30" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AH30" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AI30" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>9.0924661724045119E-2</v>
       </c>
       <c r="AJ30" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>9.0924661724045119E-2</v>
       </c>
     </row>
@@ -4545,27 +4563,27 @@
         <v>66</v>
       </c>
       <c r="F32" s="15">
-        <f>+F33-F43</f>
+        <f t="shared" ref="F32:K32" si="46">+F33-F43</f>
         <v>579.79999999999995</v>
       </c>
       <c r="G32" s="15">
-        <f>+G33-G43</f>
+        <f t="shared" si="46"/>
         <v>760.09999999999991</v>
       </c>
       <c r="H32" s="15">
-        <f>+H33-H43</f>
+        <f t="shared" si="46"/>
         <v>532.6</v>
       </c>
       <c r="I32" s="15">
-        <f>+I33-I43</f>
+        <f t="shared" si="46"/>
         <v>341.30000000000007</v>
       </c>
       <c r="J32" s="15">
-        <f>+J33-J43</f>
+        <f t="shared" si="46"/>
         <v>392.60000000000014</v>
       </c>
       <c r="K32" s="15">
-        <f>+K33-K43</f>
+        <f t="shared" si="46"/>
         <v>572.39999999999986</v>
       </c>
       <c r="AA32" s="2">
@@ -4716,27 +4734,27 @@
         <v>53</v>
       </c>
       <c r="F39" s="15">
-        <f>+SUM(F33:F38)</f>
+        <f t="shared" ref="F39:K39" si="47">+SUM(F33:F38)</f>
         <v>8283.2999999999993</v>
       </c>
       <c r="G39" s="15">
-        <f>+SUM(G33:G38)</f>
+        <f t="shared" si="47"/>
         <v>8331.1</v>
       </c>
       <c r="H39" s="15">
-        <f>+SUM(H33:H38)</f>
+        <f t="shared" si="47"/>
         <v>7885.6999999999989</v>
       </c>
       <c r="I39" s="15">
-        <f>+SUM(I33:I38)</f>
+        <f t="shared" si="47"/>
         <v>7714.6</v>
       </c>
       <c r="J39" s="15">
-        <f>+SUM(J33:J38)</f>
+        <f t="shared" si="47"/>
         <v>7917.1</v>
       </c>
       <c r="K39" s="15">
-        <f>+SUM(K33:K38)</f>
+        <f t="shared" si="47"/>
         <v>7867.9</v>
       </c>
     </row>
@@ -4837,27 +4855,27 @@
         <v>58</v>
       </c>
       <c r="F45" s="15">
-        <f>+SUM(F41:F44)</f>
+        <f t="shared" ref="F45:K45" si="48">+SUM(F41:F44)</f>
         <v>8283.2999999999993</v>
       </c>
       <c r="G45" s="15">
-        <f>+SUM(G41:G44)</f>
+        <f t="shared" si="48"/>
         <v>8331.1</v>
       </c>
       <c r="H45" s="15">
-        <f>+SUM(H41:H44)</f>
+        <f t="shared" si="48"/>
         <v>7885.7000000000007</v>
       </c>
       <c r="I45" s="15">
-        <f>+SUM(I41:I44)</f>
+        <f t="shared" si="48"/>
         <v>7714.6</v>
       </c>
       <c r="J45" s="15">
-        <f>+SUM(J41:J44)</f>
+        <f t="shared" si="48"/>
         <v>7917</v>
       </c>
       <c r="K45" s="15">
-        <f>+SUM(K41:K44)</f>
+        <f t="shared" si="48"/>
         <v>7867.9</v>
       </c>
     </row>
@@ -5042,35 +5060,35 @@
         <v>61</v>
       </c>
       <c r="C60" s="15">
-        <f t="shared" ref="C60:J60" si="38">+C58+C59</f>
+        <f t="shared" ref="C60:J60" si="49">+C58+C59</f>
         <v>752.69999999999993</v>
       </c>
       <c r="D60" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>272.59999999999997</v>
       </c>
       <c r="E60" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>249.1</v>
       </c>
       <c r="F60" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>393.2</v>
       </c>
       <c r="G60" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>338.2</v>
       </c>
       <c r="H60" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>371</v>
       </c>
       <c r="I60" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>252.70000000000002</v>
       </c>
       <c r="J60" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>144</v>
       </c>
       <c r="K60" s="15">
@@ -5087,35 +5105,35 @@
         <v>247.70000000000002</v>
       </c>
       <c r="D61" s="15">
-        <f t="shared" ref="D61:K61" si="39">+D16</f>
+        <f t="shared" ref="D61:K61" si="50">+D16</f>
         <v>183.49999999999997</v>
       </c>
       <c r="E61" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>122.70000000000005</v>
       </c>
       <c r="F61" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>193.00000000000011</v>
       </c>
       <c r="G61" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>163.79999999999995</v>
       </c>
       <c r="H61" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>88.500000000000028</v>
       </c>
       <c r="I61" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>106.70000000000002</v>
       </c>
       <c r="J61" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>143.20000000000002</v>
       </c>
       <c r="K61" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>90.80000000000004</v>
       </c>
     </row>
@@ -5124,23 +5142,23 @@
         <v>62</v>
       </c>
       <c r="F64" s="15">
-        <f t="shared" ref="F64:J64" si="40">+SUM(C60:F60)</f>
+        <f t="shared" ref="F64:J64" si="51">+SUM(C60:F60)</f>
         <v>1667.6</v>
       </c>
       <c r="G64" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>1253.0999999999999</v>
       </c>
       <c r="H64" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>1351.5</v>
       </c>
       <c r="I64" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>1355.1000000000001</v>
       </c>
       <c r="J64" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>1105.9000000000001</v>
       </c>
       <c r="K64" s="15">
@@ -5153,23 +5171,23 @@
         <v>63</v>
       </c>
       <c r="F65" s="15">
-        <f t="shared" ref="F65:J65" si="41">+SUM(C61:F61)</f>
+        <f t="shared" ref="F65:J65" si="52">+SUM(C61:F61)</f>
         <v>746.9000000000002</v>
       </c>
       <c r="G65" s="15">
-        <f t="shared" si="41"/>
+        <f t="shared" si="52"/>
         <v>663.00000000000011</v>
       </c>
       <c r="H65" s="15">
-        <f t="shared" si="41"/>
+        <f t="shared" si="52"/>
         <v>568.00000000000011</v>
       </c>
       <c r="I65" s="15">
-        <f t="shared" si="41"/>
+        <f t="shared" si="52"/>
         <v>552.00000000000011</v>
       </c>
       <c r="J65" s="15">
-        <f t="shared" si="41"/>
+        <f t="shared" si="52"/>
         <v>502.20000000000005</v>
       </c>
       <c r="K65" s="15">
